--- a/dictionary/ユーザー辞書_統合版_公開用.xlsx
+++ b/dictionary/ユーザー辞書_統合版_公開用.xlsx
@@ -4694,7 +4694,7 @@
     <t xml:space="preserve">ひょうか</t>
   </si>
   <si>
-    <t xml:space="preserve">福祉用具の利用により、動作時の身体的負担が軽減され、ご自宅での生活が安定しています。本日の用具点検でも異常はなく、引き続き安心してご利用いただける状態です。万一の不具合にもすぐに対応いたします。今後もご本人の身体状況に応じて、適宜、適切な福祉用具の選定を行ってまいります。</t>
+    <t xml:space="preserve">現在お使いの福祉用具が身体状況に合っており、無理なく安全な日常生活が送れています。今後もご本人のペースや意向を大切にしながら、必要に応じた見直しと支援を続けていきます。また、本日の用具点検でも異常はなく、引き続き安心してご利用いただけます。万一の不具合にもすぐに対応いたします。</t>
   </si>
   <si>
     <t xml:space="preserve">制限なし</t>
@@ -4768,46 +4768,46 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">福祉用具があることで動作への安心感が生まれ、日々の生活への意欲の維持につながっています。用具の点検結果も良好で、異常は見られませんでした。不具合時には迅速に点検や交換等の対応を行います。今後もご本人の「できること」を大切にし、自立した生活が続けられるよう福祉用具の活用を支援してまいります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">福祉用具を安全にご利用いただき、身体に負担をかけることなく日々の生活が送れています。用具の点検も行いましたが、異常はありませんでした。不具合発生時には迅速に対応できる体制を整えております。今後も定期的なモニタリングを行い、身体状況の変化に応じて福祉用具の見直しを行ってまいります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">福祉用具の活用により、介護するご家族の負担も軽減され、在宅での生活が安定しています。定期点検を実施し、異常がないことを確認しました。不具合が生じた際は速やかに対応いたします。引き続き、ご本人・ご家族のご意向を伺いながら、適切な福祉用具の提案を行ってまいります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">福祉用具の利用により転倒なく安全に過ごされており、ご本人の自信にもつながっています。本日の点検でも用具に異常はなく、安全にご利用いただけます。不具合時の連絡体制についても改めてお伝えしました。今後も定期的なモニタリングを行い、身体状況の変化に応じて福祉用具の見直しを行ってまいります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">用具の使い方にも慣れ、ご自身でできる動作が増えています。本日、用具の動作確認と各部の点検を行いましたが、緩みや破損はなく、良好な状態です。今後もご本人の「できること」を大切にし、自立した生活が続けられるよう福祉用具の活用を支援してまいります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">福祉用具の活用により外出の機会が増え、生活に張り合いが出てきています。定期点検で各部の固定や動作を確認し、異常がないことを確かめました。引き続き安全にご利用いただけます。季節や体調の変化による使い勝手の違いにも注意し、必要に応じて用具の調整を行ってまいります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一部の動作に不安定さが見られるようになったため、用具の調整を行いました。用具の点検でも異常は確認されず、安全な状態です。不具合時はすぐにご連絡いただくようお伝えしました。状態に変化が見られた際は、ケアマネジャーと連携し、速やかに福祉用具の変更を検討してまいります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">夜間のトイレへの移動も福祉用具の利用で安全に行えており、転倒の不安が軽減されています。用具の点検とあわせて使用状況を伺いましたが、不具合やご不便はないとのことでした。定期的な評価やメンテナンス等を通じて、身体状況に応じた福祉用具の選定を行ってまいります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">退院後の生活にも少しずつ慣れ、福祉用具を使って安全に過ごされています。用具の点検を実施しましたが、特に問題はありませんでした。お困りごとや不具合があれば速やかに対応します。身体機能の回復に応じて、用具の変更や利用の終了も含めて検討してまいります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">福祉用具の利用により、動作時の身体的負担が軽減され、ご自宅での生活が安定しています。商品の点検を行い、気になる点があればご連絡いただくようお伝えしました。また、ご本人の身体状況に応じて、適宜、適切な福祉用具の選定を行ってまいります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">福祉用具を安全にご利用いただき、身体に負担をかけることなく日々の生活が送れています。本日の用具点検でも異常はなく、引き続き安心してご利用いただける状態です。万一の不具合にもすぐに対応いたします。今後もご本人に適合した福祉用具の選定を行ってまいります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">福祉用具の利用により転倒なく安全に過ごされており、ご本人の自信にもつながっています。用具の点検結果も良好で、異常は見られませんでした。不具合時には迅速に点検や交換等の対応を行います。状態に変化が見られた際は、ケアマネジャーと連携し、速やかに福祉用具の変更を検討してまいります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">福祉用具があることで動作への安心感が生まれ、日々の生活への意欲の維持につながっています。用具の点検も行いましたが、異常はありませんでした。不具合発生時には迅速に対応できる体制を整えております。今後もご本人の身体状況に応じて、適宜、適切な福祉用具の選定を行ってまいります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">福祉用具の活用により、介護するご家族の負担も軽減され、在宅での生活が安定しています。本日、用具の動作確認と各部の点検を行いましたが、緩みや破損はなく、良好な状態です。また、ご本人の身体状況に応じて、適宜、適切な福祉用具の選定を行ってまいります。</t>
+    <t xml:space="preserve">福祉用具の利用により、動作時の身体的負担が軽減され、ご自宅での生活が安定しています。今後もご本人の身体状況に応じて、適宜、適切な福祉用具の選定を行ってまいります。また、本日の用具点検でも異常はなく、引き続き安心してご利用いただける状態です。万一の不具合にもすぐに対応いたします。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">福祉用具があることで動作への安心感が生まれ、日々の生活への意欲の維持につながっています。今後もご本人の「できること」を大切にし、自立した生活が続けられるよう福祉用具の活用を支援してまいります。また、用具の点検結果も良好で、異常は見られませんでした。不具合時には迅速に点検や交換等の対応を行います。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">福祉用具を安全にご利用いただき、身体に負担をかけることなく日々の生活が送れています。今後も定期的なモニタリングを行い、身体状況の変化に応じて福祉用具の見直しを行ってまいります。また、用具の点検も行いましたが、異常はありませんでした。不具合発生時には迅速に対応できる体制を整えております。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">福祉用具の活用により、介護するご家族の負担も軽減され、在宅での生活が安定しています。引き続き、ご本人・ご家族のご意向を伺いながら、適切な福祉用具の提案を行ってまいります。また、定期点検を実施し、異常がないことを確認しました。不具合が生じた際は速やかに対応いたします。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">福祉用具の利用により転倒なく安全に過ごされており、ご本人の自信にもつながっています。今後も定期的なモニタリングを行い、身体状況の変化に応じて福祉用具の見直しを行ってまいります。また、本日の点検でも用具に異常はなく、安全にご利用いただけます。不具合時の連絡体制についても改めてお伝えしました。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用具の使い方にも慣れ、ご自身でできる動作が増えています。今後もご本人の「できること」を大切にし、自立した生活が続けられるよう福祉用具の活用を支援してまいります。また、本日、用具の動作確認と各部の点検を行いましたが、緩みや破損はなく、良好な状態です。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">福祉用具の活用により外出の機会が増え、生活に張り合いが出てきています。季節や体調の変化による使い勝手の違いにも注意し、必要に応じて用具の調整を行ってまいります。また、定期点検で各部の固定や動作を確認し、異常がないことを確かめました。引き続き安全にご利用いただけます。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一部の動作に不安定さが見られるようになったため、用具の調整を行いました。状態に変化が見られた際は、ケアマネジャーと連携し、速やかに福祉用具の変更を検討してまいります。また、用具の点検でも異常は確認されず、安全な状態です。不具合時はすぐにご連絡いただくようお伝えしました。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">夜間のトイレへの移動も福祉用具の利用で安全に行えており、転倒の不安が軽減されています。定期的な評価やメンテナンス等を通じて、身体状況に応じた福祉用具の選定を行ってまいります。また、用具の点検とあわせて使用状況を伺いましたが、不具合やご不便はないとのことでした。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">退院後の生活にも少しずつ慣れ、福祉用具を使って安全に過ごされています。身体機能の回復に応じて、用具の変更や利用の終了も含めて検討してまいります。また、用具の点検を実施しましたが、特に問題はありませんでした。お困りごとや不具合があれば速やかに対応します。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">福祉用具を安全にご利用いただき、身体に負担をかけることなく日々の生活が送れています。今後もご本人に適合した福祉用具の選定を行ってまいります。また、本日の用具点検でも異常はなく、引き続き安心してご利用いただける状態です。万一の不具合にもすぐに対応いたします。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">福祉用具の利用により転倒なく安全に過ごされており、ご本人の自信にもつながっています。状態に変化が見られた際は、ケアマネジャーと連携し、速やかに福祉用具の変更を検討してまいります。また、用具の点検結果も良好で、異常は見られませんでした。不具合時には迅速に点検や交換等の対応を行います。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">福祉用具があることで動作への安心感が生まれ、日々の生活への意欲の維持につながっています。今後もご本人の身体状況に応じて、適宜、適切な福祉用具の選定を行ってまいります。また、用具の点検も行いましたが、異常はありませんでした。不具合発生時には迅速に対応できる体制を整えております。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">福祉用具の活用により、介護するご家族の負担も軽減され、在宅での生活が安定しています。定期的な評価やメンテナンス等を通じて、身体状況に応じた福祉用具の選定を行ってまいります。また、本日、用具の動作確認と各部の点検を行いましたが、緩みや破損はなく、良好な状態です。</t>
   </si>
   <si>
     <t xml:space="preserve">総合評価</t>
@@ -29858,7 +29858,7 @@
       </c>
       <c r="G562" s="11" t="n">
         <f aca="false">LEN(E562)</f>
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H562" s="10" t="s">
         <v>755</v>
@@ -29888,7 +29888,7 @@
       </c>
       <c r="G563" s="10" t="n">
         <f aca="false">LEN(E563)</f>
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="H563" s="10" t="s">
         <v>755</v>
@@ -29918,7 +29918,7 @@
       </c>
       <c r="G564" s="10" t="n">
         <f aca="false">LEN(E564)</f>
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H564" s="10" t="s">
         <v>755</v>
@@ -29948,7 +29948,7 @@
       </c>
       <c r="G565" s="10" t="n">
         <f aca="false">LEN(E565)</f>
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="H565" s="10" t="s">
         <v>755</v>
@@ -29978,7 +29978,7 @@
       </c>
       <c r="G566" s="10" t="n">
         <f aca="false">LEN(E566)</f>
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="H566" s="10" t="s">
         <v>755</v>
@@ -29987,7 +29987,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="567" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="567" customFormat="false" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A567" s="40" t="n">
         <v>563</v>
       </c>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="G567" s="10" t="n">
         <f aca="false">LEN(E567)</f>
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="H567" s="10" t="s">
         <v>755</v>
@@ -30017,7 +30017,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="568" customFormat="false" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="568" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A568" s="40" t="n">
         <v>564</v>
       </c>
@@ -30038,7 +30038,7 @@
       </c>
       <c r="G568" s="10" t="n">
         <f aca="false">LEN(E568)</f>
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="H568" s="10" t="s">
         <v>755</v>
@@ -30068,7 +30068,7 @@
       </c>
       <c r="G569" s="10" t="n">
         <f aca="false">LEN(E569)</f>
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H569" s="10" t="s">
         <v>755</v>
@@ -30077,7 +30077,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="570" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="570" customFormat="false" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A570" s="40" t="n">
         <v>566</v>
       </c>
@@ -30098,7 +30098,7 @@
       </c>
       <c r="G570" s="10" t="n">
         <f aca="false">LEN(E570)</f>
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="H570" s="10" t="s">
         <v>755</v>
@@ -30107,7 +30107,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="571" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="571" customFormat="false" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A571" s="40" t="n">
         <v>567</v>
       </c>
@@ -30128,7 +30128,7 @@
       </c>
       <c r="G571" s="10" t="n">
         <f aca="false">LEN(E571)</f>
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H571" s="10" t="s">
         <v>755</v>
@@ -30158,7 +30158,7 @@
       </c>
       <c r="G572" s="10" t="n">
         <f aca="false">LEN(E572)</f>
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="H572" s="10" t="s">
         <v>755</v>
@@ -30188,7 +30188,7 @@
       </c>
       <c r="G573" s="10" t="n">
         <f aca="false">LEN(E573)</f>
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H573" s="10" t="s">
         <v>755</v>
@@ -30218,7 +30218,7 @@
       </c>
       <c r="G574" s="10" t="n">
         <f aca="false">LEN(E574)</f>
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H574" s="10" t="s">
         <v>755</v>
@@ -30248,7 +30248,7 @@
       </c>
       <c r="G575" s="10" t="n">
         <f aca="false">LEN(E575)</f>
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H575" s="10" t="s">
         <v>755</v>
@@ -30257,7 +30257,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="576" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="576" customFormat="false" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A576" s="40" t="n">
         <v>572</v>
       </c>
@@ -30278,7 +30278,7 @@
       </c>
       <c r="G576" s="10" t="n">
         <f aca="false">LEN(E576)</f>
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="H576" s="10" t="s">
         <v>755</v>

--- a/dictionary/ユーザー辞書_統合版_公開用.xlsx
+++ b/dictionary/ユーザー辞書_統合版_公開用.xlsx
@@ -2865,16 +2865,16 @@
     <t xml:space="preserve">りゅうい</t>
   </si>
   <si>
-    <t xml:space="preserve">（福祉用具全般）商品に不調がある状態で使い続けると、事故やけがの原因となります。異常を感じた際は使用を中止し、担当者までご連絡ください。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（福祉用具全般）身体状況の変化などで使いにくさを感じた際は、用具の調整や変更を検討しますので、担当者までご相談ください。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（福祉用具全般）用具の改造や分解、取扱説明書と異なる使い方は、思わぬ事故の原因となるため、お控えください。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（福祉用具全般）入院や施設への入所などで使用を中止する際は、担当者またはケアマネジャーまでご連絡ください。</t>
+    <t xml:space="preserve">商品に不調がある状態で使い続けると、事故やけがの原因となります。異常を感じた際は使用を中止し、担当者までご連絡ください。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">身体状況の変化などで使いにくさを感じた際は、用具の調整や変更を検討しますので、担当者までご相談ください。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用具の改造や分解、取扱説明書と異なる使い方は、思わぬ事故の原因となるため、お控えください。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入院や施設への入所などで使用を中止する際は、担当者またはケアマネジャーまでご連絡ください。</t>
   </si>
   <si>
     <r>
@@ -7787,7 +7787,7 @@
     <t xml:space="preserve">－</t>
   </si>
   <si>
-    <t xml:space="preserve">（福祉用具全般）で始まる共通の文</t>
+    <t xml:space="preserve">用具を問わない共通の文（先頭に用具名は付けない）</t>
   </si>
   <si>
     <t xml:space="preserve">■ 提案理由</t>
@@ -11314,7 +11314,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">点です。すべての文の先頭に（手すり）（シャワーチェア）（床ずれ防止用具）のように用具名を付けています。全用具に共通の文は（福祉用具全般）で始まります。</t>
+      <t xml:space="preserve">点です。すべての文の先頭に（手すり）（シャワーチェア）（床ずれ防止用具）のように用具名を付けています。全用具に共通の文（福祉用具全般・よみ：りゅうい）には付けていません。</t>
     </r>
   </si>
   <si>
@@ -25528,7 +25528,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="423" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="423" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="27" t="n">
         <v>419</v>
       </c>
@@ -25549,7 +25549,7 @@
       </c>
       <c r="G423" s="11" t="n">
         <f aca="false">LEN(E423)</f>
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H423" s="11" t="str">
         <f aca="false">IF(G423&lt;=100,"OK","100字超")</f>
@@ -25580,7 +25580,7 @@
       </c>
       <c r="G424" s="11" t="n">
         <f aca="false">LEN(E424)</f>
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H424" s="11" t="str">
         <f aca="false">IF(G424&lt;=100,"OK","100字超")</f>
@@ -25611,7 +25611,7 @@
       </c>
       <c r="G425" s="11" t="n">
         <f aca="false">LEN(E425)</f>
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="H425" s="11" t="str">
         <f aca="false">IF(G425&lt;=100,"OK","100字超")</f>
@@ -25642,7 +25642,7 @@
       </c>
       <c r="G426" s="11" t="n">
         <f aca="false">LEN(E426)</f>
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="H426" s="11" t="str">
         <f aca="false">IF(G426&lt;=100,"OK","100字超")</f>

--- a/dictionary/ユーザー辞書_統合版_公開用.xlsx
+++ b/dictionary/ユーザー辞書_統合版_公開用.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9574" uniqueCount="1865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9574" uniqueCount="1866">
   <si>
     <r>
       <rPr>
@@ -4813,9 +4813,18 @@
     <t xml:space="preserve">総合評価</t>
   </si>
   <si>
-    <t xml:space="preserve">福祉用具の利用により、動作時の身体的負担が軽減され、ご自宅での生活が安定しています。今後もご本人のご希望を伺いながら、状況に合わせた適切な支援を継続してまいります。</t>
-  </si>
-  <si>
+    <t xml:space="preserve">福祉用具の利用により動作時の身体的負担が軽減され、ご自宅での生活が安定しています。本日の点検でも異常はなく、今後も状況に合わせた支援を継続してまいります。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF404040"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">文章を修正 ／ </t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
@@ -4856,10 +4865,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">福祉用具があることで動作への安心感が生まれ、日々の生活への意欲の維持につながっています。今後もご本人のご希望に沿って、その時々に合った福祉用具の活用を支援してまいります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">福祉用具を安全にご利用いただき、身体に負担をかけることなく日々の生活が送れています。今後もご本人のご意向を尊重し、小さな変化にも気づけるよう適宜見直しを行いながら支援を継続します。</t>
+    <t xml:space="preserve">福祉用具があることで動作への安心感が生まれ、生活への意欲の維持につながっています。用具の点検でも異常はなく、今後もご希望に沿った活用を支援してまいります。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">福祉用具を安全にご利用いただき、身体に負担なく日々の生活が送れています。点検でも異常は見られず、今後も小さな変化に気づけるよう適宜見直しを行ってまいります。</t>
   </si>
   <si>
     <r>
@@ -4911,25 +4920,25 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">福祉用具の活用により、介護するご家族の負担も軽減され、在宅での生活が安定しています。引き続き、ご本人とご家族の両方が安心して過ごせるよう支援してまいります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">福祉用具の利用により転倒なく安全に過ごされており、ご本人の自信にもつながっています。今後も身体状況の変化に注意し、必要に応じて用具の見直しを行います。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">用具の使い方にも慣れ、ご自身でできる動作が増えています。今後は活動範囲の拡大も目指し、ご本人の意欲を大切にしながら、状態に合った用具の提案を続けていきます。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">福祉用具の活用により外出の機会が増え、生活に張り合いが出てきています。今後も安全に外出を続けられるよう、使用状況や身体状況を確認しながら支援していきます。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一部の動作に不安定さが見られるようになったため、用具の調整を行いました。今後は状態の変化に注意し、ケアマネジャーと連携しながら必要に応じて用具の変更を検討します。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">夜間のトイレへの移動も福祉用具の利用で安全に行えており、転倒の不安が軽減されています。今後も夜間の様子をご家族と共有しながら、必要に応じて見直しを行います。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">退院後の生活にも少しずつ慣れ、福祉用具を使って安全に過ごされています。今後は身体状況の回復に合わせて、用具の変更や返却も含めて検討していきます。</t>
+    <t xml:space="preserve">福祉用具の活用により、介護するご家族の負担も軽減され、在宅での生活が安定しています。用具の点検結果も良好で、引き続き安心して過ごせるよう支援してまいります。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">福祉用具の利用により転倒なく安全に過ごされ、ご本人の自信にもつながっています。用具の点検でも異常はなく、今後も身体状況の変化に応じて見直しを行います。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用具の使い方にも慣れ、ご自身でできる動作が増えています。点検でも緩みや破損はなく良好です。今後もご本人の意欲を大切にし、状態に合った用具の提案を続けてまいります。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">福祉用具の活用により外出の機会が増え、生活に張り合いが出てきています。用具の点検でも異常はなく、今後も安全に外出を続けられるよう支援してまいります。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一部の動作に不安定さが見られたため、点検とあわせて用具の調整を行いました。今後は状態の変化に注意し、ケアマネジャーと連携して用具の変更も検討します。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">夜間のトイレへの移動も福祉用具の利用で安全に行えており、転倒の不安が軽減されています。点検でも異常はなく、今後も夜間の様子を確認しながら支援してまいります。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">退院後の生活にも少しずつ慣れ、福祉用具を使って安全に過ごされています。用具の点検でも異常はなく、今後は回復に合わせて用具の変更や返却も検討してまいります。</t>
   </si>
   <si>
     <t xml:space="preserve">今後の方針</t>
@@ -9113,6 +9122,9 @@
     <t xml:space="preserve">現在お使いの福祉用具が身体状況に合っており、無理なく安全な日常生活が送れています。今後もご本人のペースや意向を大切にしながら、必要に応じた見直しと支援を続けていきます。</t>
   </si>
   <si>
+    <t xml:space="preserve">福祉用具の利用により、動作時の身体的負担が軽減され、ご自宅での生活が安定しています。今後もご本人のご希望を伺いながら、状況に合わせた適切な支援を継続してまいります。</t>
+  </si>
+  <si>
     <t xml:space="preserve">福祉用具を適切に利用することで安全が保たれ、生活の負担軽減に繋がっています。今後も身体状況に応じた見直しを行いながら、在宅生活を支援していきます。</t>
   </si>
   <si>
@@ -10713,7 +10725,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">件ずつ（総合評価は今後の方針まで含めた文をさらに</t>
+      <t xml:space="preserve">件ずつ（総合評価は点検と今後の方針まで含めた</t>
     </r>
     <r>
       <rPr>
@@ -10722,7 +10734,24 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">文字以内の文に整えて</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
     </r>
     <r>
       <rPr>
@@ -30308,13 +30337,13 @@
       </c>
       <c r="G577" s="10" t="n">
         <f aca="false">LEN(E577)</f>
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H577" s="10" t="str">
         <f aca="false">IF(G577&lt;=100,"OK","100字超")</f>
         <v>OK</v>
       </c>
-      <c r="I577" s="36" t="s">
+      <c r="I577" s="12" t="s">
         <v>773</v>
       </c>
     </row>
@@ -30339,7 +30368,7 @@
       </c>
       <c r="G578" s="10" t="n">
         <f aca="false">LEN(E578)</f>
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H578" s="10" t="str">
         <f aca="false">IF(G578&lt;=100,"OK","100字超")</f>
@@ -30370,7 +30399,7 @@
       </c>
       <c r="G579" s="10" t="n">
         <f aca="false">LEN(E579)</f>
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H579" s="10" t="str">
         <f aca="false">IF(G579&lt;=100,"OK","100字超")</f>
@@ -30463,7 +30492,7 @@
       </c>
       <c r="G582" s="10" t="n">
         <f aca="false">LEN(E582)</f>
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H582" s="10" t="str">
         <f aca="false">IF(G582&lt;=100,"OK","100字超")</f>
@@ -30494,7 +30523,7 @@
       </c>
       <c r="G583" s="10" t="n">
         <f aca="false">LEN(E583)</f>
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H583" s="10" t="str">
         <f aca="false">IF(G583&lt;=100,"OK","100字超")</f>
@@ -30525,7 +30554,7 @@
       </c>
       <c r="G584" s="10" t="n">
         <f aca="false">LEN(E584)</f>
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H584" s="10" t="str">
         <f aca="false">IF(G584&lt;=100,"OK","100字超")</f>
@@ -30587,7 +30616,7 @@
       </c>
       <c r="G586" s="10" t="n">
         <f aca="false">LEN(E586)</f>
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H586" s="10" t="str">
         <f aca="false">IF(G586&lt;=100,"OK","100字超")</f>
@@ -47354,7 +47383,7 @@
       </c>
       <c r="I191" s="68"/>
     </row>
-    <row r="192" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="64" t="s">
         <v>1618</v>
       </c>
@@ -47392,10 +47421,10 @@
         <v>753</v>
       </c>
       <c r="D193" s="67" t="s">
-        <v>772</v>
+        <v>1651</v>
       </c>
       <c r="E193" s="66" t="s">
-        <v>17</v>
+        <v>1508</v>
       </c>
       <c r="F193" s="66" t="s">
         <v>753</v>
@@ -47419,7 +47448,7 @@
         <v>753</v>
       </c>
       <c r="D194" s="67" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="E194" s="66" t="s">
         <v>1565</v>
@@ -47435,7 +47464,7 @@
       </c>
       <c r="I194" s="68"/>
     </row>
-    <row r="195" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="64" t="s">
         <v>1618</v>
       </c>
@@ -47446,7 +47475,7 @@
         <v>753</v>
       </c>
       <c r="D195" s="67" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="E195" s="66" t="s">
         <v>1565</v>
@@ -47473,7 +47502,7 @@
         <v>753</v>
       </c>
       <c r="D196" s="67" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="E196" s="66" t="s">
         <v>1508</v>
@@ -47500,7 +47529,7 @@
         <v>753</v>
       </c>
       <c r="D197" s="67" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="E197" s="66" t="s">
         <v>1565</v>
@@ -47527,7 +47556,7 @@
         <v>753</v>
       </c>
       <c r="D198" s="67" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="E198" s="66" t="s">
         <v>1565</v>
@@ -47635,7 +47664,7 @@
         <v>1352</v>
       </c>
       <c r="D202" s="67" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="E202" s="66" t="s">
         <v>1626</v>
@@ -47797,7 +47826,7 @@
         <v>1410</v>
       </c>
       <c r="D208" s="67" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="E208" s="66" t="s">
         <v>1523</v>
@@ -47878,7 +47907,7 @@
         <v>1315</v>
       </c>
       <c r="D211" s="68" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="E211" s="66" t="s">
         <v>1626</v>
@@ -47905,7 +47934,7 @@
         <v>1467</v>
       </c>
       <c r="D212" s="67" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="E212" s="66" t="s">
         <v>1523</v>
@@ -47932,7 +47961,7 @@
         <v>988</v>
       </c>
       <c r="D213" s="67" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="E213" s="66" t="s">
         <v>1626</v>
@@ -47959,7 +47988,7 @@
         <v>1473</v>
       </c>
       <c r="D214" s="67" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="E214" s="66" t="s">
         <v>1523</v>
@@ -47986,7 +48015,7 @@
         <v>1332</v>
       </c>
       <c r="D215" s="68" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="E215" s="66" t="s">
         <v>17</v>
@@ -47995,7 +48024,7 @@
         <v>1332</v>
       </c>
       <c r="G215" s="68" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="H215" s="65" t="n">
         <v>863</v>
@@ -48040,7 +48069,7 @@
         <v>1146</v>
       </c>
       <c r="D217" s="67" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="E217" s="66" t="s">
         <v>1622</v>
@@ -48121,7 +48150,7 @@
         <v>1144</v>
       </c>
       <c r="D220" s="67" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="E220" s="66" t="s">
         <v>1626</v>
@@ -48148,7 +48177,7 @@
         <v>1139</v>
       </c>
       <c r="D221" s="67" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="E221" s="66" t="s">
         <v>1626</v>
@@ -48364,7 +48393,7 @@
         <v>668</v>
       </c>
       <c r="D229" s="67" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="E229" s="66" t="s">
         <v>1508</v>
@@ -48391,7 +48420,7 @@
         <v>668</v>
       </c>
       <c r="D230" s="67" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="E230" s="66" t="s">
         <v>1508</v>
@@ -48418,7 +48447,7 @@
         <v>668</v>
       </c>
       <c r="D231" s="67" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="E231" s="66" t="s">
         <v>1508</v>
@@ -48526,7 +48555,7 @@
         <v>1424</v>
       </c>
       <c r="D235" s="67" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="E235" s="66" t="s">
         <v>1565</v>
@@ -48553,7 +48582,7 @@
         <v>1424</v>
       </c>
       <c r="D236" s="67" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="E236" s="66" t="s">
         <v>1565</v>
@@ -48607,7 +48636,7 @@
         <v>1491</v>
       </c>
       <c r="D238" s="67" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="E238" s="66" t="s">
         <v>1523</v>
@@ -48634,7 +48663,7 @@
         <v>1489</v>
       </c>
       <c r="D239" s="67" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="E239" s="66" t="s">
         <v>1565</v>
@@ -48661,7 +48690,7 @@
         <v>1489</v>
       </c>
       <c r="D240" s="67" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="E240" s="66" t="s">
         <v>1523</v>
@@ -48688,7 +48717,7 @@
         <v>785</v>
       </c>
       <c r="D241" s="67" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="E241" s="66" t="s">
         <v>1508</v>
@@ -48715,7 +48744,7 @@
         <v>1207</v>
       </c>
       <c r="D242" s="67" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="E242" s="66" t="s">
         <v>1626</v>
@@ -48796,7 +48825,7 @@
         <v>1433</v>
       </c>
       <c r="D245" s="67" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="E245" s="66" t="s">
         <v>1565</v>
@@ -48850,10 +48879,10 @@
         <v>1459</v>
       </c>
       <c r="D247" s="67" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="E247" s="66" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="F247" s="66" t="s">
         <v>604</v>
@@ -48865,7 +48894,7 @@
         <v>464</v>
       </c>
       <c r="I247" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -48879,7 +48908,7 @@
         <v>1461</v>
       </c>
       <c r="D248" s="67" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="E248" s="66" t="s">
         <v>1523</v>
@@ -48894,7 +48923,7 @@
         <v>468</v>
       </c>
       <c r="I248" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -48908,7 +48937,7 @@
         <v>1461</v>
       </c>
       <c r="D249" s="67" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="E249" s="66" t="s">
         <v>1523</v>
@@ -48923,7 +48952,7 @@
         <v>469</v>
       </c>
       <c r="I249" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -48937,7 +48966,7 @@
         <v>826</v>
       </c>
       <c r="D250" s="67" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="E250" s="66" t="s">
         <v>1508</v>
@@ -48964,7 +48993,7 @@
         <v>826</v>
       </c>
       <c r="D251" s="67" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="E251" s="66" t="s">
         <v>1508</v>
@@ -48991,7 +49020,7 @@
         <v>826</v>
       </c>
       <c r="D252" s="67" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="E252" s="66" t="s">
         <v>1508</v>
@@ -49018,7 +49047,7 @@
         <v>826</v>
       </c>
       <c r="D253" s="67" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="E253" s="66" t="s">
         <v>1565</v>
@@ -49045,7 +49074,7 @@
         <v>826</v>
       </c>
       <c r="D254" s="67" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="E254" s="66" t="s">
         <v>1508</v>
@@ -49072,7 +49101,7 @@
         <v>826</v>
       </c>
       <c r="D255" s="67" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="E255" s="66" t="s">
         <v>1565</v>
@@ -49099,7 +49128,7 @@
         <v>1448</v>
       </c>
       <c r="D256" s="67" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="E256" s="66" t="s">
         <v>1523</v>
@@ -49126,10 +49155,10 @@
         <v>1451</v>
       </c>
       <c r="D257" s="67" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="E257" s="66" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="F257" s="66" t="s">
         <v>563</v>
@@ -49141,7 +49170,7 @@
         <v>441</v>
       </c>
       <c r="I257" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49155,10 +49184,10 @@
         <v>1451</v>
       </c>
       <c r="D258" s="67" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="E258" s="66" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="F258" s="66" t="s">
         <v>563</v>
@@ -49170,7 +49199,7 @@
         <v>439</v>
       </c>
       <c r="I258" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49211,7 +49240,7 @@
         <v>1450</v>
       </c>
       <c r="D260" s="67" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="E260" s="66" t="s">
         <v>1523</v>
@@ -49238,7 +49267,7 @@
         <v>640</v>
       </c>
       <c r="D261" s="67" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="E261" s="66" t="s">
         <v>1508</v>
@@ -49253,7 +49282,7 @@
         <v>483</v>
       </c>
       <c r="I261" s="67" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49294,10 +49323,10 @@
         <v>1452</v>
       </c>
       <c r="D263" s="67" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="E263" s="66" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="F263" s="66" t="s">
         <v>563</v>
@@ -49309,7 +49338,7 @@
         <v>445</v>
       </c>
       <c r="I263" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -49404,7 +49433,7 @@
         <v>1030</v>
       </c>
       <c r="D267" s="67" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="E267" s="66" t="s">
         <v>1626</v>
@@ -49413,7 +49442,7 @@
         <v>1030</v>
       </c>
       <c r="G267" s="67" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="H267" s="65" t="n">
         <v>725</v>
@@ -49431,7 +49460,7 @@
         <v>1028</v>
       </c>
       <c r="D268" s="67" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="E268" s="66" t="s">
         <v>17</v>
@@ -49440,7 +49469,7 @@
         <v>1028</v>
       </c>
       <c r="G268" s="67" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="H268" s="65" t="n">
         <v>724</v>
@@ -49485,7 +49514,7 @@
         <v>1024</v>
       </c>
       <c r="D270" s="67" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="E270" s="66" t="s">
         <v>1626</v>
@@ -49494,7 +49523,7 @@
         <v>1024</v>
       </c>
       <c r="G270" s="67" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="H270" s="65" t="n">
         <v>723</v>
@@ -49512,7 +49541,7 @@
         <v>1110</v>
       </c>
       <c r="D271" s="68" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="E271" s="66" t="s">
         <v>17</v>
@@ -49521,7 +49550,7 @@
         <v>1110</v>
       </c>
       <c r="G271" s="68" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="H271" s="65" t="n">
         <v>763</v>
@@ -49755,7 +49784,7 @@
         <v>1116</v>
       </c>
       <c r="D280" s="67" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="E280" s="66" t="s">
         <v>1626</v>
@@ -49809,7 +49838,7 @@
         <v>1312</v>
       </c>
       <c r="D282" s="68" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="E282" s="66" t="s">
         <v>1626</v>
@@ -49944,7 +49973,7 @@
         <v>1426</v>
       </c>
       <c r="D287" s="67" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="E287" s="66" t="s">
         <v>1565</v>
@@ -50079,10 +50108,10 @@
         <v>1446</v>
       </c>
       <c r="D292" s="67" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="E292" s="66" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="F292" s="66" t="s">
         <v>543</v>
@@ -50094,7 +50123,7 @@
         <v>425</v>
       </c>
       <c r="I292" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -50108,7 +50137,7 @@
         <v>813</v>
       </c>
       <c r="D293" s="67" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="E293" s="66" t="s">
         <v>1565</v>
@@ -50123,7 +50152,7 @@
         <v>603</v>
       </c>
       <c r="I293" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -50137,7 +50166,7 @@
         <v>813</v>
       </c>
       <c r="D294" s="67" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="E294" s="66" t="s">
         <v>1508</v>
@@ -50164,7 +50193,7 @@
         <v>813</v>
       </c>
       <c r="D295" s="67" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="E295" s="66" t="s">
         <v>1508</v>
@@ -50191,7 +50220,7 @@
         <v>813</v>
       </c>
       <c r="D296" s="67" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="E296" s="66" t="s">
         <v>1508</v>
@@ -50218,10 +50247,10 @@
         <v>1447</v>
       </c>
       <c r="D297" s="67" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="E297" s="66" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="F297" s="66" t="s">
         <v>543</v>
@@ -50233,7 +50262,7 @@
         <v>428</v>
       </c>
       <c r="I297" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -50247,7 +50276,7 @@
         <v>1493</v>
       </c>
       <c r="D298" s="67" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="E298" s="66" t="s">
         <v>1523</v>
@@ -50355,7 +50384,7 @@
         <v>739</v>
       </c>
       <c r="D302" s="67" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="E302" s="66" t="s">
         <v>1508</v>
@@ -50436,7 +50465,7 @@
         <v>1022</v>
       </c>
       <c r="D305" s="67" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="E305" s="66" t="s">
         <v>17</v>
@@ -50445,7 +50474,7 @@
         <v>1022</v>
       </c>
       <c r="G305" s="67" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="H305" s="65" t="n">
         <v>721</v>
@@ -50463,7 +50492,7 @@
         <v>1438</v>
       </c>
       <c r="D306" s="67" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="E306" s="66" t="s">
         <v>1565</v>
@@ -50490,10 +50519,10 @@
         <v>1405</v>
       </c>
       <c r="D307" s="67" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="E307" s="66" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="F307" s="66" t="s">
         <v>182</v>
@@ -50505,7 +50534,7 @@
         <v>136</v>
       </c>
       <c r="I307" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -50519,7 +50548,7 @@
         <v>1405</v>
       </c>
       <c r="D308" s="67" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="E308" s="66" t="s">
         <v>1565</v>
@@ -50534,7 +50563,7 @@
         <v>136</v>
       </c>
       <c r="I308" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -50602,10 +50631,10 @@
         <v>1406</v>
       </c>
       <c r="D311" s="67" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="E311" s="66" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="F311" s="66" t="s">
         <v>182</v>
@@ -50617,7 +50646,7 @@
         <v>136</v>
       </c>
       <c r="I311" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -50631,7 +50660,7 @@
         <v>1407</v>
       </c>
       <c r="D312" s="67" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="E312" s="66" t="s">
         <v>1565</v>
@@ -50646,7 +50675,7 @@
         <v>136</v>
       </c>
       <c r="I312" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -50687,7 +50716,7 @@
         <v>1444</v>
       </c>
       <c r="D314" s="67" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="E314" s="66" t="s">
         <v>1523</v>
@@ -50768,7 +50797,7 @@
         <v>1485</v>
       </c>
       <c r="D317" s="67" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="E317" s="66" t="s">
         <v>1523</v>
@@ -50822,7 +50851,7 @@
         <v>1330</v>
       </c>
       <c r="D319" s="68" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="E319" s="66" t="s">
         <v>17</v>
@@ -50831,7 +50860,7 @@
         <v>1330</v>
       </c>
       <c r="G319" s="68" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="H319" s="65" t="n">
         <v>862</v>
@@ -50849,7 +50878,7 @@
         <v>727</v>
       </c>
       <c r="D320" s="67" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="E320" s="66" t="s">
         <v>1565</v>
@@ -50903,7 +50932,7 @@
         <v>727</v>
       </c>
       <c r="D322" s="67" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="E322" s="66" t="s">
         <v>1622</v>
@@ -50930,7 +50959,7 @@
         <v>727</v>
       </c>
       <c r="D323" s="67" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="E323" s="66" t="s">
         <v>1508</v>
@@ -50957,7 +50986,7 @@
         <v>838</v>
       </c>
       <c r="D324" s="67" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="E324" s="66" t="s">
         <v>1508</v>
@@ -51038,7 +51067,7 @@
         <v>968</v>
       </c>
       <c r="D327" s="67" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="E327" s="66" t="s">
         <v>1626</v>
@@ -51092,7 +51121,7 @@
         <v>801</v>
       </c>
       <c r="D329" s="67" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="E329" s="66" t="s">
         <v>1508</v>
@@ -51119,7 +51148,7 @@
         <v>965</v>
       </c>
       <c r="D330" s="67" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="E330" s="66" t="s">
         <v>1622</v>
@@ -51200,7 +51229,7 @@
         <v>1495</v>
       </c>
       <c r="D333" s="67" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="E333" s="66" t="s">
         <v>1523</v>
@@ -51254,7 +51283,7 @@
         <v>1455</v>
       </c>
       <c r="D335" s="67" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="E335" s="66" t="s">
         <v>1523</v>
@@ -51308,7 +51337,7 @@
         <v>957</v>
       </c>
       <c r="D337" s="67" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="E337" s="66" t="s">
         <v>1626</v>
@@ -51335,7 +51364,7 @@
         <v>957</v>
       </c>
       <c r="D338" s="67" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="E338" s="66" t="s">
         <v>1626</v>
@@ -51389,7 +51418,7 @@
         <v>952</v>
       </c>
       <c r="D340" s="67" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="E340" s="66" t="s">
         <v>1626</v>
@@ -51443,7 +51472,7 @@
         <v>643</v>
       </c>
       <c r="D342" s="67" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="E342" s="66" t="s">
         <v>1508</v>
@@ -51470,10 +51499,10 @@
         <v>1458</v>
       </c>
       <c r="D343" s="67" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="E343" s="66" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="F343" s="66" t="s">
         <v>582</v>
@@ -51485,7 +51514,7 @@
         <v>453</v>
       </c>
       <c r="I343" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -51499,10 +51528,10 @@
         <v>1458</v>
       </c>
       <c r="D344" s="67" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="E344" s="66" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="F344" s="66" t="s">
         <v>582</v>
@@ -51514,7 +51543,7 @@
         <v>458</v>
       </c>
       <c r="I344" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -51528,10 +51557,10 @@
         <v>1458</v>
       </c>
       <c r="D345" s="67" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="E345" s="66" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="F345" s="66" t="s">
         <v>582</v>
@@ -51543,7 +51572,7 @@
         <v>455</v>
       </c>
       <c r="I345" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -51557,7 +51586,7 @@
         <v>1457</v>
       </c>
       <c r="D346" s="67" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="E346" s="66" t="s">
         <v>1523</v>
@@ -51719,7 +51748,7 @@
         <v>1020</v>
       </c>
       <c r="D352" s="67" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="E352" s="66" t="s">
         <v>17</v>
@@ -51728,7 +51757,7 @@
         <v>1020</v>
       </c>
       <c r="G352" s="67" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="H352" s="65" t="n">
         <v>720</v>
@@ -51746,7 +51775,7 @@
         <v>929</v>
       </c>
       <c r="D353" s="67" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="E353" s="66" t="s">
         <v>1626</v>
@@ -51827,7 +51856,7 @@
         <v>1417</v>
       </c>
       <c r="D356" s="67" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="E356" s="66" t="s">
         <v>1565</v>
@@ -52124,7 +52153,7 @@
         <v>1475</v>
       </c>
       <c r="D367" s="67" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="E367" s="66" t="s">
         <v>1523</v>
@@ -52340,7 +52369,7 @@
         <v>1488</v>
       </c>
       <c r="D375" s="67" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="E375" s="66" t="s">
         <v>1565</v>
@@ -52367,7 +52396,7 @@
         <v>1488</v>
       </c>
       <c r="D376" s="67" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="E376" s="66" t="s">
         <v>1523</v>
@@ -52448,7 +52477,7 @@
         <v>648</v>
       </c>
       <c r="D379" s="67" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="E379" s="66" t="s">
         <v>1508</v>
@@ -52502,7 +52531,7 @@
         <v>1018</v>
       </c>
       <c r="D381" s="67" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="E381" s="66" t="s">
         <v>1626</v>
@@ -52511,7 +52540,7 @@
         <v>1018</v>
       </c>
       <c r="G381" s="67" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="H381" s="65" t="n">
         <v>719</v>
@@ -52529,7 +52558,7 @@
         <v>1018</v>
       </c>
       <c r="D382" s="67" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="E382" s="66" t="s">
         <v>1622</v>
@@ -52538,7 +52567,7 @@
         <v>1018</v>
       </c>
       <c r="G382" s="67" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="H382" s="65" t="n">
         <v>719</v>
@@ -52556,7 +52585,7 @@
         <v>1018</v>
       </c>
       <c r="D383" s="67" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="E383" s="66" t="s">
         <v>1622</v>
@@ -52565,7 +52594,7 @@
         <v>1018</v>
       </c>
       <c r="G383" s="67" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="H383" s="65" t="n">
         <v>719</v>
@@ -52691,7 +52720,7 @@
         <v>1474</v>
       </c>
       <c r="D388" s="67" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="E388" s="66" t="s">
         <v>1523</v>
@@ -52718,7 +52747,7 @@
         <v>950</v>
       </c>
       <c r="D389" s="67" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="E389" s="66" t="s">
         <v>1626</v>
@@ -52745,7 +52774,7 @@
         <v>947</v>
       </c>
       <c r="D390" s="67" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="E390" s="66" t="s">
         <v>1626</v>
@@ -52772,7 +52801,7 @@
         <v>947</v>
       </c>
       <c r="D391" s="67" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="E391" s="66" t="s">
         <v>1626</v>
@@ -52799,7 +52828,7 @@
         <v>944</v>
       </c>
       <c r="D392" s="67" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="E392" s="66" t="s">
         <v>1626</v>
@@ -52826,7 +52855,7 @@
         <v>1015</v>
       </c>
       <c r="D393" s="67" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="E393" s="66" t="s">
         <v>1626</v>
@@ -52835,7 +52864,7 @@
         <v>1015</v>
       </c>
       <c r="G393" s="67" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="H393" s="65" t="n">
         <v>718</v>
@@ -52853,7 +52882,7 @@
         <v>1015</v>
       </c>
       <c r="D394" s="67" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="E394" s="66" t="s">
         <v>1622</v>
@@ -52862,7 +52891,7 @@
         <v>1015</v>
       </c>
       <c r="G394" s="67" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="H394" s="65" t="n">
         <v>718</v>
@@ -52934,7 +52963,7 @@
         <v>1102</v>
       </c>
       <c r="D397" s="68" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="E397" s="66" t="s">
         <v>1626</v>
@@ -52985,19 +53014,19 @@
         <v>324</v>
       </c>
       <c r="C399" s="66" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="D399" s="67" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="E399" s="66" t="s">
         <v>1626</v>
       </c>
       <c r="F399" s="66" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="G399" s="68" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="H399" s="65" t="n">
         <v>716</v>
@@ -53015,7 +53044,7 @@
         <v>1480</v>
       </c>
       <c r="D400" s="67" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="E400" s="66" t="s">
         <v>1622</v>
@@ -53177,7 +53206,7 @@
         <v>1328</v>
       </c>
       <c r="D406" s="68" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="E406" s="66" t="s">
         <v>17</v>
@@ -53186,7 +53215,7 @@
         <v>1328</v>
       </c>
       <c r="G406" s="68" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="H406" s="65" t="n">
         <v>861</v>
@@ -53204,7 +53233,7 @@
         <v>856</v>
       </c>
       <c r="D407" s="67" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="E407" s="66" t="s">
         <v>1508</v>
@@ -53258,7 +53287,7 @@
         <v>1009</v>
       </c>
       <c r="D409" s="67" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="E409" s="66" t="s">
         <v>1626</v>
@@ -53267,7 +53296,7 @@
         <v>1009</v>
       </c>
       <c r="G409" s="67" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="H409" s="65" t="n">
         <v>715</v>
@@ -53285,7 +53314,7 @@
         <v>1006</v>
       </c>
       <c r="D410" s="67" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="E410" s="66" t="s">
         <v>1626</v>
@@ -53294,7 +53323,7 @@
         <v>1006</v>
       </c>
       <c r="G410" s="67" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="H410" s="65" t="n">
         <v>714</v>
@@ -53309,10 +53338,10 @@
         <v>339</v>
       </c>
       <c r="C411" s="64" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="D411" s="67" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="E411" s="66" t="s">
         <v>1523</v>
@@ -53339,7 +53368,7 @@
         <v>1004</v>
       </c>
       <c r="D412" s="67" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="E412" s="66" t="s">
         <v>17</v>
@@ -53348,7 +53377,7 @@
         <v>1004</v>
       </c>
       <c r="G412" s="67" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="H412" s="65" t="n">
         <v>713</v>
@@ -53385,7 +53414,7 @@
         <v>543</v>
       </c>
       <c r="D414" s="67" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="E414" s="66" t="s">
         <v>1508</v>
@@ -53412,7 +53441,7 @@
         <v>1397</v>
       </c>
       <c r="D415" s="67" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="E415" s="66" t="s">
         <v>1523</v>
@@ -53571,10 +53600,10 @@
         <v>351</v>
       </c>
       <c r="C421" s="64" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="D421" s="67" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="E421" s="66" t="s">
         <v>1523</v>
@@ -53619,7 +53648,7 @@
     </row>
     <row r="423" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B423" s="65" t="n">
         <v>1</v>
@@ -53638,7 +53667,7 @@
     </row>
     <row r="424" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B424" s="65" t="n">
         <v>2</v>
@@ -53647,7 +53676,7 @@
         <v>543</v>
       </c>
       <c r="D424" s="67" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="E424" s="66" t="s">
         <v>1508</v>
@@ -53665,7 +53694,7 @@
     </row>
     <row r="425" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B425" s="65" t="n">
         <v>3</v>
@@ -53692,7 +53721,7 @@
     </row>
     <row r="426" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B426" s="65" t="n">
         <v>4</v>
@@ -53719,7 +53748,7 @@
     </row>
     <row r="427" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B427" s="65" t="n">
         <v>5</v>
@@ -53746,7 +53775,7 @@
     </row>
     <row r="428" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B428" s="65" t="n">
         <v>6</v>
@@ -53773,7 +53802,7 @@
     </row>
     <row r="429" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B429" s="65" t="n">
         <v>7</v>
@@ -53782,7 +53811,7 @@
         <v>563</v>
       </c>
       <c r="D429" s="67" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="E429" s="66" t="s">
         <v>1508</v>
@@ -53800,7 +53829,7 @@
     </row>
     <row r="430" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B430" s="65" t="n">
         <v>8</v>
@@ -53827,7 +53856,7 @@
     </row>
     <row r="431" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B431" s="65" t="n">
         <v>9</v>
@@ -53836,7 +53865,7 @@
         <v>563</v>
       </c>
       <c r="D431" s="67" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="E431" s="66" t="s">
         <v>1508</v>
@@ -53854,7 +53883,7 @@
     </row>
     <row r="432" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B432" s="65" t="n">
         <v>10</v>
@@ -53881,7 +53910,7 @@
     </row>
     <row r="433" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B433" s="65" t="n">
         <v>11</v>
@@ -53908,7 +53937,7 @@
     </row>
     <row r="434" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B434" s="65" t="n">
         <v>12</v>
@@ -53935,7 +53964,7 @@
     </row>
     <row r="435" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B435" s="65" t="n">
         <v>13</v>
@@ -53944,7 +53973,7 @@
         <v>582</v>
       </c>
       <c r="D435" s="67" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="E435" s="66" t="s">
         <v>1508</v>
@@ -53962,7 +53991,7 @@
     </row>
     <row r="436" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B436" s="65" t="n">
         <v>14</v>
@@ -53989,7 +54018,7 @@
     </row>
     <row r="437" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B437" s="65" t="n">
         <v>15</v>
@@ -53998,7 +54027,7 @@
         <v>604</v>
       </c>
       <c r="D437" s="67" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="E437" s="66" t="s">
         <v>1565</v>
@@ -54013,12 +54042,12 @@
         <v>463</v>
       </c>
       <c r="I437" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="438" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B438" s="65" t="n">
         <v>16</v>
@@ -54045,7 +54074,7 @@
     </row>
     <row r="439" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B439" s="65" t="n">
         <v>17</v>
@@ -54054,7 +54083,7 @@
         <v>604</v>
       </c>
       <c r="D439" s="67" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="E439" s="66" t="s">
         <v>1508</v>
@@ -54069,12 +54098,12 @@
         <v>466</v>
       </c>
       <c r="I439" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B440" s="65" t="n">
         <v>18</v>
@@ -54083,7 +54112,7 @@
         <v>604</v>
       </c>
       <c r="D440" s="67" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="E440" s="66" t="s">
         <v>1614</v>
@@ -54098,12 +54127,12 @@
         <v>466</v>
       </c>
       <c r="I440" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B441" s="65" t="n">
         <v>19</v>
@@ -54112,7 +54141,7 @@
         <v>604</v>
       </c>
       <c r="D441" s="67" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="E441" s="66" t="s">
         <v>1622</v>
@@ -54127,12 +54156,12 @@
         <v>465</v>
       </c>
       <c r="I441" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B442" s="65" t="n">
         <v>20</v>
@@ -54141,7 +54170,7 @@
         <v>604</v>
       </c>
       <c r="D442" s="67" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="E442" s="66" t="s">
         <v>1508</v>
@@ -54156,12 +54185,12 @@
         <v>467</v>
       </c>
       <c r="I442" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B443" s="65" t="n">
         <v>21</v>
@@ -54170,7 +54199,7 @@
         <v>543</v>
       </c>
       <c r="D443" s="67" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="E443" s="66" t="s">
         <v>1508</v>
@@ -54188,7 +54217,7 @@
     </row>
     <row r="444" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B444" s="65" t="n">
         <v>22</v>
@@ -54197,7 +54226,7 @@
         <v>543</v>
       </c>
       <c r="D444" s="67" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="E444" s="66" t="s">
         <v>1508</v>
@@ -54215,7 +54244,7 @@
     </row>
     <row r="445" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B445" s="65" t="n">
         <v>23</v>
@@ -54224,7 +54253,7 @@
         <v>543</v>
       </c>
       <c r="D445" s="67" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="E445" s="66" t="s">
         <v>1508</v>
@@ -54242,7 +54271,7 @@
     </row>
     <row r="446" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B446" s="65" t="n">
         <v>24</v>
@@ -54269,7 +54298,7 @@
     </row>
     <row r="447" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B447" s="65" t="n">
         <v>25</v>
@@ -54278,7 +54307,7 @@
         <v>543</v>
       </c>
       <c r="D447" s="67" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="E447" s="66" t="s">
         <v>1508</v>
@@ -54296,7 +54325,7 @@
     </row>
     <row r="448" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B448" s="65" t="n">
         <v>26</v>
@@ -54305,7 +54334,7 @@
         <v>582</v>
       </c>
       <c r="D448" s="67" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="E448" s="66" t="s">
         <v>1508</v>
@@ -54323,7 +54352,7 @@
     </row>
     <row r="449" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B449" s="65" t="n">
         <v>27</v>
@@ -54332,7 +54361,7 @@
         <v>582</v>
       </c>
       <c r="D449" s="67" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="E449" s="66" t="s">
         <v>1614</v>
@@ -54350,7 +54379,7 @@
     </row>
     <row r="450" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B450" s="65" t="n">
         <v>28</v>
@@ -54377,7 +54406,7 @@
     </row>
     <row r="451" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B451" s="65" t="n">
         <v>29</v>
@@ -54386,7 +54415,7 @@
         <v>668</v>
       </c>
       <c r="D451" s="67" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="E451" s="66" t="s">
         <v>1614</v>
@@ -54404,7 +54433,7 @@
     </row>
     <row r="452" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B452" s="65" t="n">
         <v>30</v>
@@ -54413,7 +54442,7 @@
         <v>668</v>
       </c>
       <c r="D452" s="67" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="E452" s="66" t="s">
         <v>1508</v>
@@ -54431,7 +54460,7 @@
     </row>
     <row r="453" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B453" s="65" t="n">
         <v>31</v>
@@ -54458,7 +54487,7 @@
     </row>
     <row r="454" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B454" s="65" t="n">
         <v>32</v>
@@ -54467,7 +54496,7 @@
         <v>668</v>
       </c>
       <c r="D454" s="67" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="E454" s="66" t="s">
         <v>1508</v>
@@ -54485,7 +54514,7 @@
     </row>
     <row r="455" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B455" s="65" t="n">
         <v>33</v>
@@ -54494,7 +54523,7 @@
         <v>668</v>
       </c>
       <c r="D455" s="67" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="E455" s="66" t="s">
         <v>1614</v>
@@ -54512,7 +54541,7 @@
     </row>
     <row r="456" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B456" s="65" t="n">
         <v>34</v>
@@ -54521,7 +54550,7 @@
         <v>668</v>
       </c>
       <c r="D456" s="67" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="E456" s="66" t="s">
         <v>1508</v>
@@ -54539,7 +54568,7 @@
     </row>
     <row r="457" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B457" s="65" t="n">
         <v>35</v>
@@ -54548,7 +54577,7 @@
         <v>753</v>
       </c>
       <c r="D457" s="67" t="s">
-        <v>772</v>
+        <v>1651</v>
       </c>
       <c r="E457" s="66" t="s">
         <v>1614</v>
@@ -54566,7 +54595,7 @@
     </row>
     <row r="458" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B458" s="65" t="n">
         <v>36</v>
@@ -54575,7 +54604,7 @@
         <v>753</v>
       </c>
       <c r="D458" s="67" t="s">
-        <v>772</v>
+        <v>1651</v>
       </c>
       <c r="E458" s="66" t="s">
         <v>1614</v>
@@ -54593,7 +54622,7 @@
     </row>
     <row r="459" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B459" s="65" t="n">
         <v>37</v>
@@ -54602,7 +54631,7 @@
         <v>753</v>
       </c>
       <c r="D459" s="67" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="E459" s="66" t="s">
         <v>1565</v>
@@ -54620,7 +54649,7 @@
     </row>
     <row r="460" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B460" s="65" t="n">
         <v>38</v>
@@ -54629,7 +54658,7 @@
         <v>753</v>
       </c>
       <c r="D460" s="67" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="E460" s="66" t="s">
         <v>1565</v>
@@ -54647,7 +54676,7 @@
     </row>
     <row r="461" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B461" s="65" t="n">
         <v>39</v>
@@ -54656,7 +54685,7 @@
         <v>753</v>
       </c>
       <c r="D461" s="67" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="E461" s="66" t="s">
         <v>1565</v>
@@ -54674,7 +54703,7 @@
     </row>
     <row r="462" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B462" s="65" t="n">
         <v>40</v>
@@ -54683,7 +54712,7 @@
         <v>753</v>
       </c>
       <c r="D462" s="67" t="s">
-        <v>772</v>
+        <v>1651</v>
       </c>
       <c r="E462" s="66" t="s">
         <v>1614</v>
@@ -54701,7 +54730,7 @@
     </row>
     <row r="463" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B463" s="65" t="n">
         <v>41</v>
@@ -54710,7 +54739,7 @@
         <v>864</v>
       </c>
       <c r="D463" s="67" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="E463" s="66" t="s">
         <v>1508</v>
@@ -54728,7 +54757,7 @@
     </row>
     <row r="464" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B464" s="65" t="n">
         <v>42</v>
@@ -54737,7 +54766,7 @@
         <v>864</v>
       </c>
       <c r="D464" s="67" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="E464" s="66" t="s">
         <v>1508</v>
@@ -54755,7 +54784,7 @@
     </row>
     <row r="465" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B465" s="65" t="n">
         <v>43</v>
@@ -54764,7 +54793,7 @@
         <v>864</v>
       </c>
       <c r="D465" s="67" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="E465" s="66" t="s">
         <v>1508</v>
@@ -54782,7 +54811,7 @@
     </row>
     <row r="466" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B466" s="65" t="n">
         <v>44</v>
@@ -54791,7 +54820,7 @@
         <v>864</v>
       </c>
       <c r="D466" s="67" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="E466" s="66" t="s">
         <v>1508</v>
@@ -54809,7 +54838,7 @@
     </row>
     <row r="467" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B467" s="65" t="n">
         <v>45</v>
@@ -54818,7 +54847,7 @@
         <v>864</v>
       </c>
       <c r="D467" s="67" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="E467" s="66" t="s">
         <v>1508</v>
@@ -54836,7 +54865,7 @@
     </row>
     <row r="468" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B468" s="65" t="n">
         <v>46</v>
@@ -54845,7 +54874,7 @@
         <v>864</v>
       </c>
       <c r="D468" s="67" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="E468" s="66" t="s">
         <v>1508</v>
@@ -54863,7 +54892,7 @@
     </row>
     <row r="469" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A469" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B469" s="65" t="n">
         <v>47</v>
@@ -54872,7 +54901,7 @@
         <v>864</v>
       </c>
       <c r="D469" s="67" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="E469" s="66" t="s">
         <v>1508</v>
@@ -54890,7 +54919,7 @@
     </row>
     <row r="470" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B470" s="65" t="n">
         <v>48</v>
@@ -54899,7 +54928,7 @@
         <v>864</v>
       </c>
       <c r="D470" s="67" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="E470" s="66" t="s">
         <v>1508</v>
@@ -54917,7 +54946,7 @@
     </row>
     <row r="471" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B471" s="65" t="n">
         <v>49</v>
@@ -54926,7 +54955,7 @@
         <v>864</v>
       </c>
       <c r="D471" s="67" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="E471" s="66" t="s">
         <v>1508</v>
@@ -54944,7 +54973,7 @@
     </row>
     <row r="472" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B472" s="65" t="n">
         <v>50</v>
@@ -54953,7 +54982,7 @@
         <v>864</v>
       </c>
       <c r="D472" s="67" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="E472" s="66" t="s">
         <v>1508</v>
@@ -54971,7 +55000,7 @@
     </row>
     <row r="473" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B473" s="65" t="n">
         <v>51</v>
@@ -54980,7 +55009,7 @@
         <v>753</v>
       </c>
       <c r="D473" s="67" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="E473" s="66" t="s">
         <v>1565</v>
@@ -54998,7 +55027,7 @@
     </row>
     <row r="474" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B474" s="65" t="n">
         <v>52</v>
@@ -55007,7 +55036,7 @@
         <v>753</v>
       </c>
       <c r="D474" s="67" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="E474" s="66" t="s">
         <v>1565</v>
@@ -55025,7 +55054,7 @@
     </row>
     <row r="475" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A475" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B475" s="65" t="n">
         <v>53</v>
@@ -55034,7 +55063,7 @@
         <v>753</v>
       </c>
       <c r="D475" s="67" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="E475" s="66" t="s">
         <v>1565</v>
@@ -55052,7 +55081,7 @@
     </row>
     <row r="476" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A476" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B476" s="65" t="n">
         <v>54</v>
@@ -55061,7 +55090,7 @@
         <v>563</v>
       </c>
       <c r="D476" s="67" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="E476" s="66" t="s">
         <v>1614</v>
@@ -55079,7 +55108,7 @@
     </row>
     <row r="477" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A477" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B477" s="65" t="n">
         <v>55</v>
@@ -55088,7 +55117,7 @@
         <v>563</v>
       </c>
       <c r="D477" s="67" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="E477" s="66" t="s">
         <v>1508</v>
@@ -55106,7 +55135,7 @@
     </row>
     <row r="478" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A478" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B478" s="65" t="n">
         <v>56</v>
@@ -55133,7 +55162,7 @@
     </row>
     <row r="479" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A479" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B479" s="65" t="n">
         <v>57</v>
@@ -55160,7 +55189,7 @@
     </row>
     <row r="480" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A480" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B480" s="65" t="n">
         <v>58</v>
@@ -55187,7 +55216,7 @@
     </row>
     <row r="481" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A481" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B481" s="65" t="n">
         <v>59</v>
@@ -55214,7 +55243,7 @@
     </row>
     <row r="482" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A482" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B482" s="65" t="n">
         <v>60</v>
@@ -55241,7 +55270,7 @@
     </row>
     <row r="483" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A483" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B483" s="65" t="n">
         <v>61</v>
@@ -55268,7 +55297,7 @@
     </row>
     <row r="484" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A484" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B484" s="65" t="n">
         <v>62</v>
@@ -55295,7 +55324,7 @@
     </row>
     <row r="485" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B485" s="65" t="n">
         <v>63</v>
@@ -55322,7 +55351,7 @@
     </row>
     <row r="486" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A486" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B486" s="65" t="n">
         <v>64</v>
@@ -55349,7 +55378,7 @@
     </row>
     <row r="487" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B487" s="65" t="n">
         <v>65</v>
@@ -55376,7 +55405,7 @@
     </row>
     <row r="488" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A488" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B488" s="65" t="n">
         <v>66</v>
@@ -55403,7 +55432,7 @@
     </row>
     <row r="489" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A489" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B489" s="65" t="n">
         <v>67</v>
@@ -55430,7 +55459,7 @@
     </row>
     <row r="490" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A490" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B490" s="65" t="n">
         <v>68</v>
@@ -55457,7 +55486,7 @@
     </row>
     <row r="491" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A491" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B491" s="65" t="n">
         <v>69</v>
@@ -55486,7 +55515,7 @@
     </row>
     <row r="492" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A492" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B492" s="65" t="n">
         <v>70</v>
@@ -55515,7 +55544,7 @@
     </row>
     <row r="493" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A493" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B493" s="65" t="n">
         <v>71</v>
@@ -55542,7 +55571,7 @@
     </row>
     <row r="494" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A494" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B494" s="65" t="n">
         <v>72</v>
@@ -55551,7 +55580,7 @@
         <v>652</v>
       </c>
       <c r="D494" s="67" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="E494" s="66" t="s">
         <v>1508</v>
@@ -55569,7 +55598,7 @@
     </row>
     <row r="495" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A495" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B495" s="65" t="n">
         <v>73</v>
@@ -55578,7 +55607,7 @@
         <v>652</v>
       </c>
       <c r="D495" s="67" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="E495" s="66" t="s">
         <v>1508</v>
@@ -55596,7 +55625,7 @@
     </row>
     <row r="496" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A496" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B496" s="65" t="n">
         <v>74</v>
@@ -55615,7 +55644,7 @@
     </row>
     <row r="497" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A497" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B497" s="65" t="n">
         <v>75</v>
@@ -55634,7 +55663,7 @@
     </row>
     <row r="498" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B498" s="65" t="n">
         <v>76</v>
@@ -55661,7 +55690,7 @@
     </row>
     <row r="499" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A499" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B499" s="65" t="n">
         <v>79</v>
@@ -55688,7 +55717,7 @@
     </row>
     <row r="500" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A500" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B500" s="65" t="n">
         <v>80</v>
@@ -55715,7 +55744,7 @@
     </row>
     <row r="501" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A501" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B501" s="65" t="n">
         <v>81</v>
@@ -55742,7 +55771,7 @@
     </row>
     <row r="502" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A502" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B502" s="65" t="n">
         <v>82</v>
@@ -55769,7 +55798,7 @@
     </row>
     <row r="503" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A503" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B503" s="65" t="n">
         <v>83</v>
@@ -55796,7 +55825,7 @@
     </row>
     <row r="504" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A504" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B504" s="65" t="n">
         <v>84</v>
@@ -55823,7 +55852,7 @@
     </row>
     <row r="505" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A505" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B505" s="65" t="n">
         <v>85</v>
@@ -55850,13 +55879,13 @@
     </row>
     <row r="506" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A506" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B506" s="65" t="n">
         <v>86</v>
       </c>
       <c r="C506" s="66" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="D506" s="68" t="s">
         <v>1286</v>
@@ -55877,7 +55906,7 @@
     </row>
     <row r="507" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A507" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B507" s="65" t="n">
         <v>87</v>
@@ -55904,7 +55933,7 @@
     </row>
     <row r="508" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A508" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B508" s="65" t="n">
         <v>88</v>
@@ -55931,7 +55960,7 @@
     </row>
     <row r="509" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A509" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B509" s="65" t="n">
         <v>89</v>
@@ -55958,7 +55987,7 @@
     </row>
     <row r="510" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A510" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B510" s="65" t="n">
         <v>90</v>
@@ -55985,7 +56014,7 @@
     </row>
     <row r="511" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A511" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B511" s="65" t="n">
         <v>91</v>
@@ -56007,12 +56036,12 @@
         <v>849</v>
       </c>
       <c r="I511" s="67" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="512" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A512" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B512" s="65" t="n">
         <v>94</v>
@@ -56039,7 +56068,7 @@
     </row>
     <row r="513" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A513" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B513" s="65" t="n">
         <v>95</v>
@@ -56048,7 +56077,7 @@
         <v>1042</v>
       </c>
       <c r="D513" s="67" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="E513" s="66" t="s">
         <v>1626</v>
@@ -56057,7 +56086,7 @@
         <v>1042</v>
       </c>
       <c r="G513" s="67" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="H513" s="65" t="n">
         <v>731</v>
@@ -56066,7 +56095,7 @@
     </row>
     <row r="514" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A514" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B514" s="65" t="n">
         <v>96</v>
@@ -56075,7 +56104,7 @@
         <v>1044</v>
       </c>
       <c r="D514" s="67" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="E514" s="66" t="s">
         <v>1626</v>
@@ -56084,7 +56113,7 @@
         <v>1044</v>
       </c>
       <c r="G514" s="67" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="H514" s="65" t="n">
         <v>732</v>
@@ -56093,7 +56122,7 @@
     </row>
     <row r="515" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A515" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B515" s="65" t="n">
         <v>97</v>
@@ -56120,7 +56149,7 @@
     </row>
     <row r="516" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A516" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B516" s="65" t="n">
         <v>98</v>
@@ -56147,7 +56176,7 @@
     </row>
     <row r="517" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A517" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B517" s="65" t="n">
         <v>99</v>
@@ -56174,7 +56203,7 @@
     </row>
     <row r="518" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A518" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B518" s="65" t="n">
         <v>100</v>
@@ -56201,7 +56230,7 @@
     </row>
     <row r="519" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A519" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B519" s="65" t="n">
         <v>101</v>
@@ -56210,7 +56239,7 @@
         <v>1142</v>
       </c>
       <c r="D519" s="67" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="E519" s="66" t="s">
         <v>1622</v>
@@ -56228,7 +56257,7 @@
     </row>
     <row r="520" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A520" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B520" s="65" t="n">
         <v>102</v>
@@ -56255,16 +56284,16 @@
     </row>
     <row r="521" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A521" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B521" s="65" t="n">
         <v>103</v>
       </c>
       <c r="C521" s="64" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D521" s="67" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="E521" s="66" t="s">
         <v>1598</v>
@@ -56282,7 +56311,7 @@
     </row>
     <row r="522" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A522" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B522" s="65" t="n">
         <v>104</v>
@@ -56291,7 +56320,7 @@
         <v>1392</v>
       </c>
       <c r="D522" s="67" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="E522" s="66" t="s">
         <v>1523</v>
@@ -56309,7 +56338,7 @@
     </row>
     <row r="523" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A523" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B523" s="65" t="n">
         <v>105</v>
@@ -56318,7 +56347,7 @@
         <v>1394</v>
       </c>
       <c r="D523" s="67" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="E523" s="66" t="s">
         <v>1598</v>
@@ -56336,7 +56365,7 @@
     </row>
     <row r="524" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A524" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B524" s="65" t="n">
         <v>106</v>
@@ -56355,7 +56384,7 @@
     </row>
     <row r="525" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A525" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B525" s="65" t="n">
         <v>107</v>
@@ -56374,7 +56403,7 @@
     </row>
     <row r="526" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A526" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B526" s="65" t="n">
         <v>108</v>
@@ -56401,7 +56430,7 @@
     </row>
     <row r="527" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A527" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B527" s="65" t="n">
         <v>109</v>
@@ -56428,7 +56457,7 @@
     </row>
     <row r="528" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A528" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B528" s="65" t="n">
         <v>110</v>
@@ -56455,7 +56484,7 @@
     </row>
     <row r="529" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A529" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B529" s="65" t="n">
         <v>111</v>
@@ -56482,7 +56511,7 @@
     </row>
     <row r="530" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A530" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B530" s="65" t="n">
         <v>112</v>
@@ -56509,7 +56538,7 @@
     </row>
     <row r="531" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A531" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B531" s="65" t="n">
         <v>113</v>
@@ -56536,7 +56565,7 @@
     </row>
     <row r="532" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A532" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B532" s="65" t="n">
         <v>114</v>
@@ -56545,7 +56574,7 @@
         <v>1403</v>
       </c>
       <c r="D532" s="67" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="E532" s="66" t="s">
         <v>1523</v>
@@ -56563,7 +56592,7 @@
     </row>
     <row r="533" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A533" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B533" s="65" t="n">
         <v>115</v>
@@ -56590,7 +56619,7 @@
     </row>
     <row r="534" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A534" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B534" s="65" t="n">
         <v>116</v>
@@ -56617,7 +56646,7 @@
     </row>
     <row r="535" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A535" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B535" s="65" t="n">
         <v>117</v>
@@ -56644,7 +56673,7 @@
     </row>
     <row r="536" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A536" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B536" s="65" t="n">
         <v>118</v>
@@ -56671,7 +56700,7 @@
     </row>
     <row r="537" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A537" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B537" s="65" t="n">
         <v>119</v>
@@ -56698,7 +56727,7 @@
     </row>
     <row r="538" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A538" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B538" s="65" t="n">
         <v>120</v>
@@ -56725,7 +56754,7 @@
     </row>
     <row r="539" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A539" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B539" s="65" t="n">
         <v>121</v>
@@ -56752,7 +56781,7 @@
     </row>
     <row r="540" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A540" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B540" s="65" t="n">
         <v>124</v>
@@ -56761,7 +56790,7 @@
         <v>1405</v>
       </c>
       <c r="D540" s="67" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="E540" s="66" t="s">
         <v>1523</v>
@@ -56779,7 +56808,7 @@
     </row>
     <row r="541" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A541" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B541" s="65" t="n">
         <v>125</v>
@@ -56806,7 +56835,7 @@
     </row>
     <row r="542" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A542" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B542" s="65" t="n">
         <v>126</v>
@@ -56833,7 +56862,7 @@
     </row>
     <row r="543" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A543" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B543" s="65" t="n">
         <v>128</v>
@@ -56860,7 +56889,7 @@
     </row>
     <row r="544" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A544" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B544" s="65" t="n">
         <v>129</v>
@@ -56887,7 +56916,7 @@
     </row>
     <row r="545" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A545" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B545" s="65" t="n">
         <v>130</v>
@@ -56914,7 +56943,7 @@
     </row>
     <row r="546" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A546" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B546" s="65" t="n">
         <v>132</v>
@@ -56941,7 +56970,7 @@
     </row>
     <row r="547" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A547" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B547" s="65" t="n">
         <v>133</v>
@@ -56968,7 +56997,7 @@
     </row>
     <row r="548" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A548" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B548" s="65" t="n">
         <v>134</v>
@@ -56995,7 +57024,7 @@
     </row>
     <row r="549" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A549" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B549" s="65" t="n">
         <v>135</v>
@@ -57004,7 +57033,7 @@
         <v>1107</v>
       </c>
       <c r="D549" s="68" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="E549" s="66" t="s">
         <v>1626</v>
@@ -57013,7 +57042,7 @@
         <v>1107</v>
       </c>
       <c r="G549" s="68" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="H549" s="65" t="n">
         <v>762</v>
@@ -57022,7 +57051,7 @@
     </row>
     <row r="550" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A550" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B550" s="65" t="n">
         <v>136</v>
@@ -57049,7 +57078,7 @@
     </row>
     <row r="551" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A551" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B551" s="65" t="n">
         <v>137</v>
@@ -57076,7 +57105,7 @@
     </row>
     <row r="552" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A552" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B552" s="65" t="n">
         <v>138</v>
@@ -57103,7 +57132,7 @@
     </row>
     <row r="553" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A553" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B553" s="65" t="n">
         <v>139</v>
@@ -57112,7 +57141,7 @@
         <v>1398</v>
       </c>
       <c r="D553" s="67" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="E553" s="66" t="s">
         <v>1523</v>
@@ -57130,7 +57159,7 @@
     </row>
     <row r="554" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A554" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B554" s="65" t="n">
         <v>140</v>
@@ -57139,7 +57168,7 @@
         <v>1416</v>
       </c>
       <c r="D554" s="67" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="E554" s="66" t="s">
         <v>1523</v>
@@ -57157,7 +57186,7 @@
     </row>
     <row r="555" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A555" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B555" s="65" t="n">
         <v>144</v>
@@ -57166,7 +57195,7 @@
         <v>1325</v>
       </c>
       <c r="D555" s="68" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="E555" s="66" t="s">
         <v>1626</v>
@@ -57175,7 +57204,7 @@
         <v>1325</v>
       </c>
       <c r="G555" s="68" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="H555" s="65" t="n">
         <v>860</v>
@@ -57184,7 +57213,7 @@
     </row>
     <row r="556" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A556" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B556" s="65" t="n">
         <v>147</v>
@@ -57211,7 +57240,7 @@
     </row>
     <row r="557" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A557" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B557" s="65" t="n">
         <v>148</v>
@@ -57238,7 +57267,7 @@
     </row>
     <row r="558" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A558" s="64" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B558" s="65" t="n">
         <v>149</v>
@@ -57265,7 +57294,7 @@
     </row>
     <row r="559" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A559" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B559" s="65" t="n">
         <v>1</v>
@@ -57284,7 +57313,7 @@
     </row>
     <row r="560" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A560" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B560" s="65" t="n">
         <v>2</v>
@@ -57293,7 +57322,7 @@
         <v>543</v>
       </c>
       <c r="D560" s="67" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="E560" s="66" t="s">
         <v>1614</v>
@@ -57311,7 +57340,7 @@
     </row>
     <row r="561" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A561" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B561" s="65" t="n">
         <v>3</v>
@@ -57338,7 +57367,7 @@
     </row>
     <row r="562" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A562" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B562" s="65" t="n">
         <v>4</v>
@@ -57365,7 +57394,7 @@
     </row>
     <row r="563" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A563" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B563" s="65" t="n">
         <v>5</v>
@@ -57392,7 +57421,7 @@
     </row>
     <row r="564" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A564" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B564" s="65" t="n">
         <v>6</v>
@@ -57419,7 +57448,7 @@
     </row>
     <row r="565" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A565" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B565" s="65" t="n">
         <v>7</v>
@@ -57428,7 +57457,7 @@
         <v>563</v>
       </c>
       <c r="D565" s="67" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="E565" s="66" t="s">
         <v>1614</v>
@@ -57446,7 +57475,7 @@
     </row>
     <row r="566" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A566" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B566" s="65" t="n">
         <v>8</v>
@@ -57473,7 +57502,7 @@
     </row>
     <row r="567" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A567" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B567" s="65" t="n">
         <v>9</v>
@@ -57482,7 +57511,7 @@
         <v>563</v>
       </c>
       <c r="D567" s="67" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="E567" s="66" t="s">
         <v>1614</v>
@@ -57500,7 +57529,7 @@
     </row>
     <row r="568" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A568" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B568" s="65" t="n">
         <v>10</v>
@@ -57527,7 +57556,7 @@
     </row>
     <row r="569" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A569" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B569" s="65" t="n">
         <v>11</v>
@@ -57554,7 +57583,7 @@
     </row>
     <row r="570" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A570" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B570" s="65" t="n">
         <v>12</v>
@@ -57581,7 +57610,7 @@
     </row>
     <row r="571" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A571" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B571" s="65" t="n">
         <v>13</v>
@@ -57590,7 +57619,7 @@
         <v>582</v>
       </c>
       <c r="D571" s="67" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="E571" s="66" t="s">
         <v>1614</v>
@@ -57608,7 +57637,7 @@
     </row>
     <row r="572" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A572" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B572" s="65" t="n">
         <v>14</v>
@@ -57635,7 +57664,7 @@
     </row>
     <row r="573" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A573" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B573" s="65" t="n">
         <v>15</v>
@@ -57644,7 +57673,7 @@
         <v>604</v>
       </c>
       <c r="D573" s="67" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="E573" s="66" t="s">
         <v>1508</v>
@@ -57662,7 +57691,7 @@
     </row>
     <row r="574" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A574" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B574" s="65" t="n">
         <v>16</v>
@@ -57689,7 +57718,7 @@
     </row>
     <row r="575" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A575" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B575" s="65" t="n">
         <v>17</v>
@@ -57698,7 +57727,7 @@
         <v>604</v>
       </c>
       <c r="D575" s="67" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="E575" s="66" t="s">
         <v>1508</v>
@@ -57716,7 +57745,7 @@
     </row>
     <row r="576" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A576" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B576" s="65" t="n">
         <v>18</v>
@@ -57725,7 +57754,7 @@
         <v>543</v>
       </c>
       <c r="D576" s="67" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="E576" s="66" t="s">
         <v>1614</v>
@@ -57743,7 +57772,7 @@
     </row>
     <row r="577" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A577" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B577" s="65" t="n">
         <v>19</v>
@@ -57752,7 +57781,7 @@
         <v>543</v>
       </c>
       <c r="D577" s="67" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="E577" s="66" t="s">
         <v>1614</v>
@@ -57770,7 +57799,7 @@
     </row>
     <row r="578" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A578" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B578" s="65" t="n">
         <v>20</v>
@@ -57779,7 +57808,7 @@
         <v>543</v>
       </c>
       <c r="D578" s="67" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="E578" s="66" t="s">
         <v>1614</v>
@@ -57797,7 +57826,7 @@
     </row>
     <row r="579" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A579" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B579" s="65" t="n">
         <v>21</v>
@@ -57824,7 +57853,7 @@
     </row>
     <row r="580" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A580" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B580" s="65" t="n">
         <v>22</v>
@@ -57833,7 +57862,7 @@
         <v>543</v>
       </c>
       <c r="D580" s="67" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="E580" s="66" t="s">
         <v>1614</v>
@@ -57851,7 +57880,7 @@
     </row>
     <row r="581" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A581" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B581" s="65" t="n">
         <v>23</v>
@@ -57860,7 +57889,7 @@
         <v>582</v>
       </c>
       <c r="D581" s="67" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="E581" s="66" t="s">
         <v>1614</v>
@@ -57878,7 +57907,7 @@
     </row>
     <row r="582" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A582" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B582" s="65" t="n">
         <v>24</v>
@@ -57887,7 +57916,7 @@
         <v>582</v>
       </c>
       <c r="D582" s="67" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="E582" s="66" t="s">
         <v>1614</v>
@@ -57905,7 +57934,7 @@
     </row>
     <row r="583" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A583" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B583" s="65" t="n">
         <v>25</v>
@@ -57932,7 +57961,7 @@
     </row>
     <row r="584" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A584" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B584" s="65" t="n">
         <v>26</v>
@@ -57941,7 +57970,7 @@
         <v>668</v>
       </c>
       <c r="D584" s="67" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="E584" s="66" t="s">
         <v>1614</v>
@@ -57959,7 +57988,7 @@
     </row>
     <row r="585" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A585" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B585" s="65" t="n">
         <v>27</v>
@@ -57968,7 +57997,7 @@
         <v>668</v>
       </c>
       <c r="D585" s="67" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="E585" s="66" t="s">
         <v>1614</v>
@@ -57986,7 +58015,7 @@
     </row>
     <row r="586" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A586" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B586" s="65" t="n">
         <v>28</v>
@@ -58013,7 +58042,7 @@
     </row>
     <row r="587" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A587" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B587" s="65" t="n">
         <v>29</v>
@@ -58022,7 +58051,7 @@
         <v>668</v>
       </c>
       <c r="D587" s="67" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="E587" s="66" t="s">
         <v>1614</v>
@@ -58040,7 +58069,7 @@
     </row>
     <row r="588" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A588" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B588" s="65" t="n">
         <v>30</v>
@@ -58049,7 +58078,7 @@
         <v>668</v>
       </c>
       <c r="D588" s="67" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="E588" s="66" t="s">
         <v>1614</v>
@@ -58067,7 +58096,7 @@
     </row>
     <row r="589" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A589" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B589" s="65" t="n">
         <v>31</v>
@@ -58076,7 +58105,7 @@
         <v>668</v>
       </c>
       <c r="D589" s="67" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="E589" s="66" t="s">
         <v>1614</v>
@@ -58094,7 +58123,7 @@
     </row>
     <row r="590" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A590" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B590" s="65" t="n">
         <v>32</v>
@@ -58103,7 +58132,7 @@
         <v>753</v>
       </c>
       <c r="D590" s="67" t="s">
-        <v>772</v>
+        <v>1651</v>
       </c>
       <c r="E590" s="66" t="s">
         <v>1614</v>
@@ -58121,7 +58150,7 @@
     </row>
     <row r="591" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A591" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B591" s="65" t="n">
         <v>33</v>
@@ -58130,7 +58159,7 @@
         <v>753</v>
       </c>
       <c r="D591" s="67" t="s">
-        <v>772</v>
+        <v>1651</v>
       </c>
       <c r="E591" s="66" t="s">
         <v>1614</v>
@@ -58148,7 +58177,7 @@
     </row>
     <row r="592" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A592" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B592" s="65" t="n">
         <v>34</v>
@@ -58157,7 +58186,7 @@
         <v>753</v>
       </c>
       <c r="D592" s="67" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="E592" s="66" t="s">
         <v>1565</v>
@@ -58175,7 +58204,7 @@
     </row>
     <row r="593" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A593" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B593" s="65" t="n">
         <v>35</v>
@@ -58184,7 +58213,7 @@
         <v>753</v>
       </c>
       <c r="D593" s="67" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="E593" s="66" t="s">
         <v>1565</v>
@@ -58202,7 +58231,7 @@
     </row>
     <row r="594" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A594" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B594" s="65" t="n">
         <v>36</v>
@@ -58211,7 +58240,7 @@
         <v>753</v>
       </c>
       <c r="D594" s="67" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="E594" s="66" t="s">
         <v>1565</v>
@@ -58229,7 +58258,7 @@
     </row>
     <row r="595" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A595" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B595" s="65" t="n">
         <v>37</v>
@@ -58238,7 +58267,7 @@
         <v>753</v>
       </c>
       <c r="D595" s="67" t="s">
-        <v>772</v>
+        <v>1651</v>
       </c>
       <c r="E595" s="66" t="s">
         <v>1614</v>
@@ -58256,7 +58285,7 @@
     </row>
     <row r="596" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A596" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B596" s="65" t="n">
         <v>38</v>
@@ -58265,7 +58294,7 @@
         <v>864</v>
       </c>
       <c r="D596" s="67" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="E596" s="66" t="s">
         <v>1614</v>
@@ -58283,7 +58312,7 @@
     </row>
     <row r="597" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A597" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B597" s="65" t="n">
         <v>39</v>
@@ -58292,7 +58321,7 @@
         <v>864</v>
       </c>
       <c r="D597" s="67" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="E597" s="66" t="s">
         <v>1614</v>
@@ -58310,7 +58339,7 @@
     </row>
     <row r="598" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A598" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B598" s="65" t="n">
         <v>40</v>
@@ -58319,7 +58348,7 @@
         <v>864</v>
       </c>
       <c r="D598" s="67" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="E598" s="66" t="s">
         <v>1614</v>
@@ -58337,7 +58366,7 @@
     </row>
     <row r="599" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A599" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B599" s="65" t="n">
         <v>41</v>
@@ -58346,7 +58375,7 @@
         <v>864</v>
       </c>
       <c r="D599" s="67" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="E599" s="66" t="s">
         <v>1614</v>
@@ -58364,7 +58393,7 @@
     </row>
     <row r="600" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A600" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B600" s="65" t="n">
         <v>42</v>
@@ -58373,7 +58402,7 @@
         <v>864</v>
       </c>
       <c r="D600" s="67" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="E600" s="66" t="s">
         <v>1614</v>
@@ -58391,7 +58420,7 @@
     </row>
     <row r="601" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A601" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B601" s="65" t="n">
         <v>43</v>
@@ -58400,7 +58429,7 @@
         <v>864</v>
       </c>
       <c r="D601" s="67" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="E601" s="66" t="s">
         <v>1614</v>
@@ -58418,7 +58447,7 @@
     </row>
     <row r="602" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A602" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B602" s="65" t="n">
         <v>44</v>
@@ -58427,7 +58456,7 @@
         <v>864</v>
       </c>
       <c r="D602" s="67" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="E602" s="66" t="s">
         <v>1614</v>
@@ -58445,7 +58474,7 @@
     </row>
     <row r="603" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A603" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B603" s="65" t="n">
         <v>45</v>
@@ -58454,7 +58483,7 @@
         <v>864</v>
       </c>
       <c r="D603" s="67" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="E603" s="66" t="s">
         <v>1614</v>
@@ -58472,7 +58501,7 @@
     </row>
     <row r="604" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A604" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B604" s="65" t="n">
         <v>46</v>
@@ -58481,7 +58510,7 @@
         <v>864</v>
       </c>
       <c r="D604" s="67" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="E604" s="66" t="s">
         <v>1614</v>
@@ -58499,7 +58528,7 @@
     </row>
     <row r="605" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A605" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B605" s="65" t="n">
         <v>47</v>
@@ -58508,7 +58537,7 @@
         <v>864</v>
       </c>
       <c r="D605" s="67" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="E605" s="66" t="s">
         <v>1614</v>
@@ -58526,7 +58555,7 @@
     </row>
     <row r="606" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A606" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B606" s="65" t="n">
         <v>48</v>
@@ -58535,7 +58564,7 @@
         <v>753</v>
       </c>
       <c r="D606" s="67" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="E606" s="66" t="s">
         <v>1565</v>
@@ -58553,7 +58582,7 @@
     </row>
     <row r="607" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A607" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B607" s="65" t="n">
         <v>49</v>
@@ -58562,7 +58591,7 @@
         <v>753</v>
       </c>
       <c r="D607" s="67" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="E607" s="66" t="s">
         <v>1565</v>
@@ -58580,7 +58609,7 @@
     </row>
     <row r="608" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A608" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B608" s="65" t="n">
         <v>50</v>
@@ -58589,7 +58618,7 @@
         <v>753</v>
       </c>
       <c r="D608" s="67" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="E608" s="66" t="s">
         <v>1565</v>
@@ -58607,7 +58636,7 @@
     </row>
     <row r="609" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A609" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B609" s="65" t="n">
         <v>51</v>
@@ -58616,7 +58645,7 @@
         <v>563</v>
       </c>
       <c r="D609" s="67" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="E609" s="66" t="s">
         <v>1614</v>
@@ -58634,7 +58663,7 @@
     </row>
     <row r="610" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A610" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B610" s="65" t="n">
         <v>52</v>
@@ -58643,7 +58672,7 @@
         <v>563</v>
       </c>
       <c r="D610" s="67" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="E610" s="66" t="s">
         <v>1614</v>
@@ -58661,7 +58690,7 @@
     </row>
     <row r="611" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A611" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B611" s="65" t="n">
         <v>53</v>
@@ -58688,7 +58717,7 @@
     </row>
     <row r="612" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A612" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B612" s="65" t="n">
         <v>54</v>
@@ -58715,7 +58744,7 @@
     </row>
     <row r="613" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A613" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B613" s="65" t="n">
         <v>55</v>
@@ -58742,7 +58771,7 @@
     </row>
     <row r="614" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A614" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B614" s="65" t="n">
         <v>56</v>
@@ -58769,7 +58798,7 @@
     </row>
     <row r="615" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A615" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B615" s="65" t="n">
         <v>57</v>
@@ -58796,7 +58825,7 @@
     </row>
     <row r="616" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A616" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B616" s="65" t="n">
         <v>58</v>
@@ -58823,7 +58852,7 @@
     </row>
     <row r="617" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A617" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B617" s="65" t="n">
         <v>59</v>
@@ -58850,7 +58879,7 @@
     </row>
     <row r="618" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A618" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B618" s="65" t="n">
         <v>60</v>
@@ -58877,7 +58906,7 @@
     </row>
     <row r="619" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A619" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B619" s="65" t="n">
         <v>61</v>
@@ -58904,7 +58933,7 @@
     </row>
     <row r="620" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A620" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B620" s="65" t="n">
         <v>62</v>
@@ -58931,7 +58960,7 @@
     </row>
     <row r="621" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A621" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B621" s="65" t="n">
         <v>63</v>
@@ -58958,7 +58987,7 @@
     </row>
     <row r="622" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A622" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B622" s="65" t="n">
         <v>64</v>
@@ -58985,7 +59014,7 @@
     </row>
     <row r="623" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A623" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B623" s="65" t="n">
         <v>65</v>
@@ -59012,7 +59041,7 @@
     </row>
     <row r="624" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A624" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B624" s="65" t="n">
         <v>66</v>
@@ -59041,7 +59070,7 @@
     </row>
     <row r="625" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A625" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B625" s="65" t="n">
         <v>67</v>
@@ -59070,7 +59099,7 @@
     </row>
     <row r="626" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A626" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B626" s="65" t="n">
         <v>68</v>
@@ -59097,7 +59126,7 @@
     </row>
     <row r="627" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A627" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B627" s="65" t="n">
         <v>69</v>
@@ -59106,7 +59135,7 @@
         <v>652</v>
       </c>
       <c r="D627" s="67" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="E627" s="66" t="s">
         <v>1614</v>
@@ -59124,7 +59153,7 @@
     </row>
     <row r="628" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A628" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B628" s="65" t="n">
         <v>70</v>
@@ -59133,7 +59162,7 @@
         <v>652</v>
       </c>
       <c r="D628" s="67" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="E628" s="66" t="s">
         <v>1614</v>
@@ -59151,7 +59180,7 @@
     </row>
     <row r="629" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A629" s="66" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B629" s="65" t="n">
         <v>71</v>
@@ -59196,142 +59225,142 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="56" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="69" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="70" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="C4" s="61" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="70" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="C5" s="71" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="70" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="C6" s="61" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="119.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="70" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="C7" s="61" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="70" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="C8" s="61" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="69" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="70" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="C11" s="61" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="70" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="C12" s="61" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="70" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="C13" s="61" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="70" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="C14" s="61" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="69" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="70" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="C17" s="61" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="70" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="C18" s="61" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="70" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="C19" s="61" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="70" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="C20" s="61" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="70" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="C21" s="61" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="70" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="C22" s="61" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -59339,97 +59368,97 @@
         <v>1258</v>
       </c>
       <c r="C23" s="61" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="69" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="70" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="C26" s="61" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="70" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="C27" s="61" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="70" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="C28" s="61" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="70" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="C29" s="61" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="70" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="C30" s="61" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="70" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="C31" s="61" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="70" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="C32" s="61" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="69" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="70" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="C35" s="71" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="70" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="C36" s="61" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="70" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="C37" s="61" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
     </row>
   </sheetData>

--- a/dictionary/ユーザー辞書_統合版_公開用.xlsx
+++ b/dictionary/ユーザー辞書_統合版_公開用.xlsx
@@ -4697,13 +4697,13 @@
     <t xml:space="preserve">ひょうか</t>
   </si>
   <si>
-    <t xml:space="preserve">現在の福祉用具が身体状況に合っており、安全な日常生活が送れています。今後もご本人の意向を大切に、適宜、見直しと支援を続けていきます。また、本日の点検でも異常はなく、不具合時もすぐに対応いたします。</t>
+    <t xml:space="preserve">現在の福祉用具が身体状況に合っており、安全な日常生活が送れています。今後もご本人の意向を伺い、適宜、見直しと支援を続けていきます。また、本日の点検でも異常はなく、不具合時もすぐに対応いたします。</t>
   </si>
   <si>
     <t xml:space="preserve">福祉用具の利用で動作の負担が軽減され、在宅生活が安定しています。今後も身体状況に応じて、適宜、適切な用具を選定してまいります。また、本日の用具点検でも異常はなく、不具合時もすぐに対応いたします。</t>
   </si>
   <si>
-    <t xml:space="preserve">福祉用具により動作に安心感が生まれ、生活への意欲も保たれています。今後も「できること」を大切に、適宜、用具の活用を支援します。また、点検結果も良好で、不具合時は迅速に点検・交換を行います。</t>
+    <t xml:space="preserve">福祉用具の利用で立ち座りや移動が安定し、安全に生活されています。今後もご様子を確認しながら、適宜、用具の利用を支援してまいります。また、点検結果も良好で、不具合時は迅速に点検・交換を行います。</t>
   </si>
   <si>
     <t xml:space="preserve">福祉用具を安全に使用され、身体に負担なく生活が送れています。今後も定期的なモニタリングで、適宜、用具を見直してまいります。また、用具の点検でも異常はなく、不具合時も迅速に対応できる体制です。</t>
@@ -4712,16 +4712,16 @@
     <t xml:space="preserve">福祉用具によりご家族の介護負担も減り、在宅生活が安定しています。ご本人・ご家族の意向を伺い、適宜、用具を提案してまいります。また、定期点検を実施し、異常がないことを確認しました。</t>
   </si>
   <si>
-    <t xml:space="preserve">福祉用具の利用で転倒なく過ごされ、自信にもつながっています。今後も身体状況の変化に応じ、適宜、用具を見直してまいります。また、本日の点検でも異常はなく、不具合時の連絡先もお伝えしました。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">用具の使い方にも慣れ、ご自身でできる動作が増えています。今後も「できること」を大切に、適宜、用具の活用を支援します。また、動作確認と各部の点検を行い、緩みや破損はなく良好な状態です。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">福祉用具の活用で外出の機会が増え、生活に張り合いが出ています。季節や体調の変化にも注意し、適宜、用具を調整してまいります。また、各部の固定や動作を点検し、異常がないことを確かめました。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一部の動作に不安定さが見られたため、用具の調整を行いました。変化があればケアマネジャーと連携し、適宜、用具の変更を検討します。また、点検で異常はなく、不具合時はすぐご連絡いただくようお伝えしました。</t>
+    <t xml:space="preserve">福祉用具の利用で転倒なく、安全に移動されています。今後も身体状況の変化に応じ、適宜、用具を見直してまいります。また、本日の点検でも異常はなく、不具合時の連絡先もお伝えしました。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用具の使い方にも慣れ、ご自身でできる動作が増えています。今後もご様子を確認しながら、適宜、用具の利用を支援してまいります。また、動作確認と各部の点検を行い、緩みや破損はなく良好な状態です。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">福祉用具の活用で、通院や買い物などの外出が増えています。季節や体調の変化にも注意し、適宜、用具を調整してまいります。また、各部の固定や動作を点検し、異常がないことを確かめました。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一部の動作に不安定さが見られたため、用具の調整を行いました。変化があればケアマネジャー様と連携し、適宜、用具を見直します。また、点検で異常はなく、不具合時はすぐご連絡いただくようお伝えしました。</t>
   </si>
   <si>
     <t xml:space="preserve">夜間のトイレ移動も福祉用具で安全に行え、転倒の不安が減っています。定期的な評価とメンテナンスで、適宜、用具を見直してまいります。また、点検とあわせて使用状況を伺い、不具合はないとのことでした。</t>
@@ -4733,10 +4733,10 @@
     <t xml:space="preserve">福祉用具を安全に使用され、身体に負担なく生活が送れています。今後もご本人に合った用具を、適宜、選定してまいります。また、本日の用具点検でも異常はなく、不具合時もすぐに対応いたします。</t>
   </si>
   <si>
-    <t xml:space="preserve">福祉用具の利用で転倒なく過ごされ、自信にもつながっています。変化があればケアマネジャーと連携し、適宜、用具の変更を検討します。また、点検結果も良好で、不具合時は迅速に点検・交換を行います。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">福祉用具により動作に安心感が生まれ、生活への意欲も保たれています。今後も身体状況に応じて、適宜、適切な用具を選定してまいります。また、用具の点検でも異常はなく、不具合時も迅速に対応できる体制です。</t>
+    <t xml:space="preserve">福祉用具の利用で転倒なく、安全に移動されています。変化があればケアマネジャー様と連携し、適宜、用具を見直します。また、点検結果も良好で、不具合時は迅速に点検・交換を行います。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">福祉用具の利用で立ち座りや移動が安定し、安全に生活されています。今後も身体状況に応じて、適宜、適切な用具を選定してまいります。また、用具の点検でも異常はなく、不具合時も迅速に対応できる体制です。</t>
   </si>
   <si>
     <t xml:space="preserve">福祉用具によりご家族の介護負担も減り、在宅生活が安定しています。定期的な評価とメンテナンスで、適宜、用具を見直してまいります。また、動作確認と各部の点検を行い、緩みや破損はなく良好な状態です。</t>
@@ -4797,10 +4797,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">福祉用具があることで動作への安心感が生まれ、生活への意欲の維持につながっています。用具の点検でも異常はなく、今後もご希望に沿った活用を支援してまいります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">福祉用具を安全にご利用いただき、身体に負担なく日々の生活が送れています。点検でも異常は見られず、今後も小さな変化に気づけるよう適宜見直しを行ってまいります。</t>
+    <t xml:space="preserve">福祉用具の利用により立ち座りや移動が安定し、安全に生活されています。用具の点検でも異常はなく、今後もご希望に沿った活用を支援してまいります。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">福祉用具を安全にご利用いただき、身体に負担なく日々の生活が送れています。点検でも異常は見られず、今後も状態を確認しながら、適宜見直しを行ってまいります。</t>
   </si>
   <si>
     <r>
@@ -4855,16 +4855,16 @@
     <t xml:space="preserve">福祉用具の活用により、介護するご家族の負担も軽減され、在宅での生活が安定しています。用具の点検結果も良好で、引き続き安心して過ごせるよう支援してまいります。</t>
   </si>
   <si>
-    <t xml:space="preserve">福祉用具の利用により転倒なく安全に過ごされ、ご本人の自信にもつながっています。用具の点検でも異常はなく、今後も身体状況の変化に応じて見直しを行います。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">用具の使い方にも慣れ、ご自身でできる動作が増えています。点検でも緩みや破損はなく良好です。今後もご本人の意欲を大切にし、状態に合った用具の提案を続けてまいります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">福祉用具の活用により外出の機会が増え、生活に張り合いが出てきています。用具の点検でも異常はなく、今後も安全に外出を続けられるよう支援してまいります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一部の動作に不安定さが見られたため、点検とあわせて用具の調整を行いました。今後は状態の変化に注意し、ケアマネジャーと連携して用具の変更も検討します。</t>
+    <t xml:space="preserve">福祉用具の利用により転倒なく、安全に移動されています。用具の点検でも異常はなく、今後も身体状況の変化に応じて見直しを行います。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用具の使い方にも慣れ、ご自身でできる動作が増えています。点検でも緩みや破損はなく良好です。今後も状態に合った用具の提案を続けてまいります。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">福祉用具の活用により、通院や買い物などの外出が増えています。用具の点検でも異常はなく、今後も安全に外出を続けられるよう支援してまいります。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一部の動作に不安定さが見られたため、点検とあわせて用具の調整を行いました。今後は状態の変化に注意し、ケアマネジャー様と連携して用具の変更も検討します。</t>
   </si>
   <si>
     <t xml:space="preserve">夜間のトイレへの移動も福祉用具の利用で安全に行えており、転倒の不安が軽減されています。点検でも異常はなく、今後も夜間の様子を確認しながら支援してまいります。</t>
@@ -4958,7 +4958,7 @@
     <t xml:space="preserve">状態に変化が見られた際は、ケアマネジャーと連携し、速やかに福祉用具の変更を検討してまいります。</t>
   </si>
   <si>
-    <t xml:space="preserve">今後もご本人の「できること」を大切にし、自立した生活が続けられるよう福祉用具の活用を支援してまいります。</t>
+    <t xml:space="preserve">今後もご自身で行える動作を続けられるよう、福祉用具の活用を支援してまいります。</t>
   </si>
   <si>
     <t xml:space="preserve">季節や体調の変化による使い勝手の違いにも注意し、必要に応じて用具の調整を行ってまいります。</t>
@@ -11362,7 +11362,7 @@
     <t xml:space="preserve">担当者会議などで、ケアマネージャーや関係者と相談・確認した内容を担当者が記録する文（です・ます調）。「更新担当者会議。〜」で始まる短い文は、である調のメモ用です。</t>
   </si>
   <si>
-    <t xml:space="preserve">担当者がモニタリングの結果をケアマネジャー等へ報告・記録する文。</t>
+    <t xml:space="preserve">担当者がモニタリングの結果をケアマネジャー等へ報告・記録する文。評価（ひょうか）の文は「ケアマネジャー様」と書き、「できることを大切に」のような大げさな言い回しは使わず、今の様子・今後の方針・点検の結果を事実のまま書いています。</t>
   </si>
   <si>
     <t xml:space="preserve">ご本人が担当者に話した言葉として、へりくだり過ぎない自然な話し言葉にしています。</t>
@@ -29844,7 +29844,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="562" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="562" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A562" s="40" t="n">
         <v>558</v>
       </c>
@@ -29865,7 +29865,7 @@
       </c>
       <c r="G562" s="11" t="n">
         <f aca="false">LEN(E562)</f>
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H562" s="11" t="str">
         <f aca="false">IF(G562&lt;=100,"OK","100字超")</f>
@@ -29927,7 +29927,7 @@
       </c>
       <c r="G564" s="11" t="n">
         <f aca="false">LEN(E564)</f>
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H564" s="11" t="str">
         <f aca="false">IF(G564&lt;=100,"OK","100字超")</f>
@@ -30020,7 +30020,7 @@
       </c>
       <c r="G567" s="11" t="n">
         <f aca="false">LEN(E567)</f>
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H567" s="11" t="str">
         <f aca="false">IF(G567&lt;=100,"OK","100字超")</f>
@@ -30051,7 +30051,7 @@
       </c>
       <c r="G568" s="11" t="n">
         <f aca="false">LEN(E568)</f>
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H568" s="11" t="str">
         <f aca="false">IF(G568&lt;=100,"OK","100字超")</f>
@@ -30082,7 +30082,7 @@
       </c>
       <c r="G569" s="11" t="n">
         <f aca="false">LEN(E569)</f>
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H569" s="11" t="str">
         <f aca="false">IF(G569&lt;=100,"OK","100字超")</f>
@@ -30092,7 +30092,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="570" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="570" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A570" s="40" t="n">
         <v>566</v>
       </c>
@@ -30113,7 +30113,7 @@
       </c>
       <c r="G570" s="11" t="n">
         <f aca="false">LEN(E570)</f>
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H570" s="11" t="str">
         <f aca="false">IF(G570&lt;=100,"OK","100字超")</f>
@@ -30237,7 +30237,7 @@
       </c>
       <c r="G574" s="11" t="n">
         <f aca="false">LEN(E574)</f>
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H574" s="11" t="str">
         <f aca="false">IF(G574&lt;=100,"OK","100字超")</f>
@@ -30247,7 +30247,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="575" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="575" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A575" s="40" t="n">
         <v>571</v>
       </c>
@@ -30268,7 +30268,7 @@
       </c>
       <c r="G575" s="11" t="n">
         <f aca="false">LEN(E575)</f>
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H575" s="11" t="str">
         <f aca="false">IF(G575&lt;=100,"OK","100字超")</f>
@@ -30361,7 +30361,7 @@
       </c>
       <c r="G578" s="11" t="n">
         <f aca="false">LEN(E578)</f>
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H578" s="11" t="str">
         <f aca="false">IF(G578&lt;=100,"OK","100字超")</f>
@@ -30392,7 +30392,7 @@
       </c>
       <c r="G579" s="11" t="n">
         <f aca="false">LEN(E579)</f>
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H579" s="11" t="str">
         <f aca="false">IF(G579&lt;=100,"OK","100字超")</f>
@@ -30433,7 +30433,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="581" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="581" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A581" s="40" t="n">
         <v>577</v>
       </c>
@@ -30454,7 +30454,7 @@
       </c>
       <c r="G581" s="11" t="n">
         <f aca="false">LEN(E581)</f>
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="H581" s="11" t="str">
         <f aca="false">IF(G581&lt;=100,"OK","100字超")</f>
@@ -30485,7 +30485,7 @@
       </c>
       <c r="G582" s="11" t="n">
         <f aca="false">LEN(E582)</f>
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="H582" s="11" t="str">
         <f aca="false">IF(G582&lt;=100,"OK","100字超")</f>
@@ -30516,7 +30516,7 @@
       </c>
       <c r="G583" s="11" t="n">
         <f aca="false">LEN(E583)</f>
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H583" s="11" t="str">
         <f aca="false">IF(G583&lt;=100,"OK","100字超")</f>
@@ -30547,7 +30547,7 @@
       </c>
       <c r="G584" s="11" t="n">
         <f aca="false">LEN(E584)</f>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H584" s="11" t="str">
         <f aca="false">IF(G584&lt;=100,"OK","100字超")</f>
@@ -30857,7 +30857,7 @@
       </c>
       <c r="G594" s="11" t="n">
         <f aca="false">LEN(E594)</f>
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H594" s="11" t="str">
         <f aca="false">IF(G594&lt;=100,"OK","100字超")</f>
@@ -59679,7 +59679,7 @@
         <v>1891</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="70" t="s">
         <v>1880</v>
       </c>
